--- a/ExperimentoCompleto.xlsx
+++ b/ExperimentoCompleto.xlsx
@@ -1,21 +1,129 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1E8FA8D-9DA8-49A9-8B44-6CDFAF63A8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E07583D-6AF2-4BF7-AF0A-CD6086101DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
+    <sheet name="Planilha2" sheetId="5" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Planilha1!$H$35</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.100" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.101" hidden="1">Planilha1!$U$1</definedName>
+    <definedName name="_xlchart.v1.102" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.103" hidden="1">Planilha1!$X$1</definedName>
+    <definedName name="_xlchart.v1.104" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">Planilha1!$I$1</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">Planilha1!$K$3:$K$31</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">Planilha1!$I$1</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">Planilha1!$K$3:$K$31</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.57" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.58" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.59" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.60" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.61" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.62" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.63" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.64" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.65" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.66" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.67" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.68" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.69" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.70" hidden="1">Planilha1!$I$1</definedName>
+    <definedName name="_xlchart.v1.71" hidden="1">Planilha1!$K$3:$K$31</definedName>
+    <definedName name="_xlchart.v1.72" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.73" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.74" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.75" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.76" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.77" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.78" hidden="1">Planilha1!$AA$1</definedName>
+    <definedName name="_xlchart.v1.79" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.80" hidden="1">Planilha1!$AD$1</definedName>
+    <definedName name="_xlchart.v1.81" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.82" hidden="1">Planilha1!$AG$1</definedName>
+    <definedName name="_xlchart.v1.83" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.84" hidden="1">Planilha1!$AJ$1</definedName>
+    <definedName name="_xlchart.v1.85" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.86" hidden="1">Planilha1!$AM$1</definedName>
+    <definedName name="_xlchart.v1.87" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.88" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.89" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.90" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.91" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.92" hidden="1">Planilha1!$I$1</definedName>
+    <definedName name="_xlchart.v1.93" hidden="1">Planilha1!$K$3:$K$31</definedName>
+    <definedName name="_xlchart.v1.94" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.95" hidden="1">Planilha1!$L$1</definedName>
+    <definedName name="_xlchart.v1.96" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.97" hidden="1">Planilha1!$O$1</definedName>
+    <definedName name="_xlchart.v1.98" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.99" hidden="1">Planilha1!$R$1</definedName>
+  </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -328,9 +436,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="171" formatCode="0.00000"/>
-    <numFmt numFmtId="172" formatCode="0.00;[Red]0.00"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.00;[Red]0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -457,7 +564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -468,6 +575,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -480,34 +594,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,6 +625,979 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.89</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.91</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.96</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.98</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="4">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.100</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="5">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.102</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="6">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.104</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="7">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.79</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="8">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.81</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="9">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.83</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="10">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.85</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="11">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.87</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="12">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.94</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>grafico desvio padrao</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:rPr>
+            <a:t>grafico desvio padrao</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{F027B10E-9D4A-42C2-A360-996EFF7CDC29}" formatIdx="0">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.88</cx:f>
+              <cx:v>Padrão</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{25922C5E-E129-4246-B9EF-39947B99D9C5}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.90</cx:f>
+              <cx:v>Irace Geral</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{8DA59056-C9D5-427C-8AA4-463B2127A648}" formatIdx="2">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.95</cx:f>
+              <cx:v>Configuracao 2 16 7 1656 63656 2,09 1</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{16C9E66D-30A4-4E13-91E8-ED12B2DB9FDE}" formatIdx="3">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.97</cx:f>
+              <cx:v>Configuracao 2 18 6 2542 73603 2,03 0</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{F2D5FD8D-045E-43AE-B8C5-E64209EAA869}" formatIdx="4">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.99</cx:f>
+              <cx:v>Configuracao  2 10 16 1644 24767 2,96 1</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="4"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{17BC3A71-22EB-47CC-B52A-284F6EFA9E05}" formatIdx="5">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.101</cx:f>
+              <cx:v>Configuração  2 14 13 2405 43525 0,87 1</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="5"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{5F522F99-7A97-4E23-9D13-87A6755777B4}" formatIdx="6">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.103</cx:f>
+              <cx:v>Configuração  2 14 19 1795 66816 2,77 0</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="6"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{971181E6-C471-4560-9CA5-01A74C68C9D8}" formatIdx="7">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.78</cx:f>
+              <cx:v>Configuração  2 20 20 1079 55559 1,08 0</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="7"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{CC135088-7A79-4E02-B37B-A1F392DFA551}" formatIdx="8">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.80</cx:f>
+              <cx:v>Configuração  2 18 13 2520 13214 0,67 1</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="8"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{3B130AD7-A71E-4A58-8854-C53F8AA3DE5E}" formatIdx="9">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.82</cx:f>
+              <cx:v>Configuração  2 11 16 1797 24360 2,34 0</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="9"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{6D41FE1A-A51D-419E-8C75-BC8EA43C68DD}" formatIdx="10">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.84</cx:f>
+              <cx:v>Configuração  2 11 17 2326 31236 1,35 1</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="10"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{1324BC5E-E88F-457C-8C14-B953E60EF5EE}" formatIdx="11">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.86</cx:f>
+              <cx:v>Configuração  2 19 6 2851 43903 1,75 0</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="11"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{CF456752-E8AB-4A6C-A2A8-C4D80D7BE8AF}" formatIdx="12">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>Irace separado</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="12"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:title/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="100.14999999999999" min="99.349999999999994"/>
+        <cx:title/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+        <cx:spPr>
+          <a:ln w="12700">
+            <a:noFill/>
+          </a:ln>
+        </cx:spPr>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr>
+                <a:ln>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:noFill/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:noFill/>
+              <a:latin typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0">
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:sysClr>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </cx:txPr>
+    </cx:legend>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E89937F0-9DA7-4960-A9AE-71155BA67E94}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="487680" y="144780"/>
+              <a:ext cx="9845040" cy="4526280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -860,57 +1934,57 @@
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="9"/>
+      <c r="E1" s="14"/>
       <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="12"/>
+      <c r="K1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="12"/>
+      <c r="M1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="6" t="s">
+      <c r="N1" s="12"/>
+      <c r="O1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="6" t="s">
+      <c r="P1" s="12"/>
+      <c r="Q1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="R1" s="7"/>
-      <c r="S1" s="6" t="s">
+      <c r="R1" s="12"/>
+      <c r="S1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="T1" s="7"/>
-      <c r="U1" s="6" t="s">
+      <c r="T1" s="12"/>
+      <c r="U1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="V1" s="7"/>
-      <c r="W1" s="6" t="s">
+      <c r="V1" s="12"/>
+      <c r="W1" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="6" t="s">
+      <c r="X1" s="12"/>
+      <c r="Y1" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Z1" s="7"/>
+      <c r="Z1" s="12"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
@@ -1072,7 +2146,7 @@
         <v>114205.4</v>
       </c>
       <c r="AB3">
-        <f>AVERAGE(
+        <f t="shared" ref="AB3:AB32" si="0">AVERAGE(
     ABS(B3-AVERAGE(B3,D3,H3,J3,L3,N3,P3,R3,T3,V3,X3,Z3)),
     ABS(D3-AVERAGE(B3,D3,H3,J3,L3,N3,P3,R3,T3,V3,X3,Z3)),
     ABS(H3-AVERAGE(B3,D3,H3,J3,L3,N3,P3,R3,T3,V3,X3,Z3)),
@@ -1171,21 +2245,7 @@
         <v>113990.39999999999</v>
       </c>
       <c r="AB4">
-        <f>AVERAGE(
-    ABS(B4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(D4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(H4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(J4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(L4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(N4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(P4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(R4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(T4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(V4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(X4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)),
-    ABS(Z4-AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4))
-)
-/AVERAGE(B4,D4,H4,J4,L4,N4,P4,R4,T4,V4,X4,Z4)</f>
+        <f t="shared" si="0"/>
         <v>7.8491535140574637E-4</v>
       </c>
     </row>
@@ -1266,21 +2326,7 @@
         <v>114199.6</v>
       </c>
       <c r="AB5">
-        <f>AVERAGE(
-    ABS(B5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(D5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(H5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(J5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(L5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(N5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(P5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(R5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(T5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(V5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(X5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)),
-    ABS(Z5-AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5))
-)
-/AVERAGE(B5,D5,H5,J5,L5,N5,P5,R5,T5,V5,X5,Z5)</f>
+        <f t="shared" si="0"/>
         <v>7.9043400136462967E-4</v>
       </c>
     </row>
@@ -1361,21 +2407,7 @@
         <v>114143.4</v>
       </c>
       <c r="AB6">
-        <f>AVERAGE(
-    ABS(B6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(D6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(H6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(J6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(L6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(N6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(P6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(R6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(T6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(V6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(X6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)),
-    ABS(Z6-AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6))
-)
-/AVERAGE(B6,D6,H6,J6,L6,N6,P6,R6,T6,V6,X6,Z6)</f>
+        <f t="shared" si="0"/>
         <v>1.0269832950817136E-3</v>
       </c>
     </row>
@@ -1456,21 +2488,7 @@
         <v>114097.2</v>
       </c>
       <c r="AB7">
-        <f>AVERAGE(
-    ABS(B7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(D7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(H7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(J7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(L7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(N7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(P7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(R7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(T7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(V7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(X7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)),
-    ABS(Z7-AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7))
-)
-/AVERAGE(B7,D7,H7,J7,L7,N7,P7,R7,T7,V7,X7,Z7)</f>
+        <f t="shared" si="0"/>
         <v>9.6725107857042287E-4</v>
       </c>
     </row>
@@ -1551,21 +2569,7 @@
         <v>114073.9</v>
       </c>
       <c r="AB8">
-        <f>AVERAGE(
-    ABS(B8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(D8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(H8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(J8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(L8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(N8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(P8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(R8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(T8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(V8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(X8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)),
-    ABS(Z8-AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8))
-)
-/AVERAGE(B8,D8,H8,J8,L8,N8,P8,R8,T8,V8,X8,Z8)</f>
+        <f t="shared" si="0"/>
         <v>9.7045837608900683E-4</v>
       </c>
     </row>
@@ -1646,21 +2650,7 @@
         <v>114085.3</v>
       </c>
       <c r="AB9">
-        <f>AVERAGE(
-    ABS(B9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(D9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(H9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(J9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(L9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(N9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(P9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(R9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(T9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(V9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(X9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)),
-    ABS(Z9-AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9))
-)
-/AVERAGE(B9,D9,H9,J9,L9,N9,P9,R9,T9,V9,X9,Z9)</f>
+        <f t="shared" si="0"/>
         <v>1.1703304591716985E-3</v>
       </c>
     </row>
@@ -1741,21 +2731,7 @@
         <v>114217.7</v>
       </c>
       <c r="AB10">
-        <f>AVERAGE(
-    ABS(B10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(D10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(H10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(J10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(L10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(N10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(P10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(R10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(T10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(V10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(X10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)),
-    ABS(Z10-AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10))
-)
-/AVERAGE(B10,D10,H10,J10,L10,N10,P10,R10,T10,V10,X10,Z10)</f>
+        <f t="shared" si="0"/>
         <v>9.8612751697493015E-4</v>
       </c>
     </row>
@@ -1836,21 +2812,7 @@
         <v>114274.8</v>
       </c>
       <c r="AB11">
-        <f>AVERAGE(
-    ABS(B11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(D11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(H11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(J11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(L11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(N11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(P11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(R11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(T11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(V11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(X11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)),
-    ABS(Z11-AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11))
-)
-/AVERAGE(B11,D11,H11,J11,L11,N11,P11,R11,T11,V11,X11,Z11)</f>
+        <f t="shared" si="0"/>
         <v>9.8157291432404985E-4</v>
       </c>
     </row>
@@ -1931,21 +2893,7 @@
         <v>114190.2</v>
       </c>
       <c r="AB12">
-        <f>AVERAGE(
-    ABS(B12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(D12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(H12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(J12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(L12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(N12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(P12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(R12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(T12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(V12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(X12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)),
-    ABS(Z12-AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12))
-)
-/AVERAGE(B12,D12,H12,J12,L12,N12,P12,R12,T12,V12,X12,Z12)</f>
+        <f t="shared" si="0"/>
         <v>9.1706375804760166E-4</v>
       </c>
     </row>
@@ -2026,21 +2974,7 @@
         <v>11281054.720000001</v>
       </c>
       <c r="AB13">
-        <f>AVERAGE(
-    ABS(B13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(D13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(H13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(J13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(L13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(N13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(P13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(R13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(T13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(V13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(X13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)),
-    ABS(Z13-AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13))
-)
-/AVERAGE(B13,D13,H13,J13,L13,N13,P13,R13,T13,V13,X13,Z13)</f>
+        <f t="shared" si="0"/>
         <v>0.16482706399054234</v>
       </c>
     </row>
@@ -2121,21 +3055,7 @@
         <v>11280858.779999999</v>
       </c>
       <c r="AB14">
-        <f>AVERAGE(
-    ABS(B14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(D14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(H14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(J14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(L14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(N14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(P14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(R14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(T14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(V14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(X14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)),
-    ABS(Z14-AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14))
-)
-/AVERAGE(B14,D14,H14,J14,L14,N14,P14,R14,T14,V14,X14,Z14)</f>
+        <f t="shared" si="0"/>
         <v>5.8407432782949344E-4</v>
       </c>
     </row>
@@ -2216,21 +3136,7 @@
         <v>11292660.41</v>
       </c>
       <c r="AB15">
-        <f>AVERAGE(
-    ABS(B15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(D15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(H15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(J15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(L15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(N15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(P15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(R15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(T15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(V15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(X15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)),
-    ABS(Z15-AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15))
-)
-/AVERAGE(B15,D15,H15,J15,L15,N15,P15,R15,T15,V15,X15,Z15)</f>
+        <f t="shared" si="0"/>
         <v>6.4765775011369376E-4</v>
       </c>
     </row>
@@ -2311,21 +3217,7 @@
         <v>11279360.15</v>
       </c>
       <c r="AB16">
-        <f>AVERAGE(
-    ABS(B16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(D16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(H16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(J16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(L16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(N16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(P16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(R16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(T16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(V16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(X16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)),
-    ABS(Z16-AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16))
-)
-/AVERAGE(B16,D16,H16,J16,L16,N16,P16,R16,T16,V16,X16,Z16)</f>
+        <f t="shared" si="0"/>
         <v>4.6781435450491364E-4</v>
       </c>
     </row>
@@ -2406,21 +3298,7 @@
         <v>11295312.51</v>
       </c>
       <c r="AB17">
-        <f>AVERAGE(
-    ABS(B17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(D17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(H17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(J17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(L17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(N17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(P17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(R17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(T17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(V17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(X17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)),
-    ABS(Z17-AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17))
-)
-/AVERAGE(B17,D17,H17,J17,L17,N17,P17,R17,T17,V17,X17,Z17)</f>
+        <f t="shared" si="0"/>
         <v>6.0384830526082056E-4</v>
       </c>
     </row>
@@ -2501,21 +3379,7 @@
         <v>11277285.529999999</v>
       </c>
       <c r="AB18">
-        <f>AVERAGE(
-    ABS(B18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(D18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(H18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(J18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(L18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(N18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(P18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(R18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(T18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(V18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(X18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)),
-    ABS(Z18-AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18))
-)
-/AVERAGE(B18,D18,H18,J18,L18,N18,P18,R18,T18,V18,X18,Z18)</f>
+        <f t="shared" si="0"/>
         <v>6.279596762265899E-4</v>
       </c>
     </row>
@@ -2596,21 +3460,7 @@
         <v>11282922.67</v>
       </c>
       <c r="AB19">
-        <f>AVERAGE(
-    ABS(B19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(D19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(H19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(J19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(L19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(N19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(P19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(R19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(T19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(V19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(X19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)),
-    ABS(Z19-AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19))
-)
-/AVERAGE(B19,D19,H19,J19,L19,N19,P19,R19,T19,V19,X19,Z19)</f>
+        <f t="shared" si="0"/>
         <v>5.5135257961599058E-4</v>
       </c>
     </row>
@@ -2691,21 +3541,7 @@
         <v>11295838.119999999</v>
       </c>
       <c r="AB20">
-        <f>AVERAGE(
-    ABS(B20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(D20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(H20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(J20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(L20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(N20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(P20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(R20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(T20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(V20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(X20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)),
-    ABS(Z20-AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20))
-)
-/AVERAGE(B20,D20,H20,J20,L20,N20,P20,R20,T20,V20,X20,Z20)</f>
+        <f t="shared" si="0"/>
         <v>5.1924519161818496E-4</v>
       </c>
     </row>
@@ -2786,21 +3622,7 @@
         <v>11289084.279999999</v>
       </c>
       <c r="AB21">
-        <f>AVERAGE(
-    ABS(B21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(D21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(H21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(J21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(L21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(N21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(P21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(R21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(T21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(V21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(X21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)),
-    ABS(Z21-AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21))
-)
-/AVERAGE(B21,D21,H21,J21,L21,N21,P21,R21,T21,V21,X21,Z21)</f>
+        <f t="shared" si="0"/>
         <v>5.8414412917615435E-4</v>
       </c>
     </row>
@@ -2881,21 +3703,7 @@
         <v>11300139.630000001</v>
       </c>
       <c r="AB22">
-        <f>AVERAGE(
-    ABS(B22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(D22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(H22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(J22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(L22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(N22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(P22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(R22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(T22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(V22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(X22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)),
-    ABS(Z22-AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22))
-)
-/AVERAGE(B22,D22,H22,J22,L22,N22,P22,R22,T22,V22,X22,Z22)</f>
+        <f t="shared" si="0"/>
         <v>6.3700090945688944E-4</v>
       </c>
     </row>
@@ -2976,21 +3784,7 @@
         <v>24884959.899999999</v>
       </c>
       <c r="AB23">
-        <f>AVERAGE(
-    ABS(B23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(D23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(H23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(J23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(L23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(N23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(P23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(R23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(T23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(V23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(X23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)),
-    ABS(Z23-AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23))
-)
-/AVERAGE(B23,D23,H23,J23,L23,N23,P23,R23,T23,V23,X23,Z23)</f>
+        <f t="shared" si="0"/>
         <v>5.5580505711305792E-4</v>
       </c>
     </row>
@@ -3071,21 +3865,7 @@
         <v>24883666.5</v>
       </c>
       <c r="AB24">
-        <f>AVERAGE(
-    ABS(B24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(D24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(H24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(J24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(L24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(N24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(P24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(R24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(T24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(V24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(X24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)),
-    ABS(Z24-AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24))
-)
-/AVERAGE(B24,D24,H24,J24,L24,N24,P24,R24,T24,V24,X24,Z24)</f>
+        <f t="shared" si="0"/>
         <v>5.6705433540624889E-4</v>
       </c>
     </row>
@@ -3166,21 +3946,7 @@
         <v>43407362.200000003</v>
       </c>
       <c r="AB25">
-        <f>AVERAGE(
-    ABS(B25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(D25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(H25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(J25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(L25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(N25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(P25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(R25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(T25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(V25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(X25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)),
-    ABS(Z25-AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25))
-)
-/AVERAGE(B25,D25,H25,J25,L25,N25,P25,R25,T25,V25,X25,Z25)</f>
+        <f t="shared" si="0"/>
         <v>4.1203792498426472E-4</v>
       </c>
     </row>
@@ -3261,21 +4027,7 @@
         <v>43437712.200000003</v>
       </c>
       <c r="AB26">
-        <f>AVERAGE(
-    ABS(B26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(D26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(H26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(J26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(L26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(N26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(P26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(R26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(T26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(V26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(X26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)),
-    ABS(Z26-AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26))
-)
-/AVERAGE(B26,D26,H26,J26,L26,N26,P26,R26,T26,V26,X26,Z26)</f>
+        <f t="shared" si="0"/>
         <v>5.0445885725252239E-4</v>
       </c>
     </row>
@@ -3356,21 +4108,7 @@
         <v>43419557.200000003</v>
       </c>
       <c r="AB27">
-        <f>AVERAGE(
-    ABS(B27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(D27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(H27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(J27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(L27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(N27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(P27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(R27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(T27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(V27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(X27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)),
-    ABS(Z27-AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27))
-)
-/AVERAGE(B27,D27,H27,J27,L27,N27,P27,R27,T27,V27,X27,Z27)</f>
+        <f t="shared" si="0"/>
         <v>6.1473205813584184E-4</v>
       </c>
     </row>
@@ -3451,21 +4189,7 @@
         <v>66972199</v>
       </c>
       <c r="AB28">
-        <f>AVERAGE(
-    ABS(B28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(D28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(H28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(J28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(L28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(N28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(P28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(R28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(T28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(V28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(X28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)),
-    ABS(Z28-AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28))
-)
-/AVERAGE(B28,D28,H28,J28,L28,N28,P28,R28,T28,V28,X28,Z28)</f>
+        <f t="shared" si="0"/>
         <v>3.3915963130750373E-4</v>
       </c>
     </row>
@@ -3546,21 +4270,7 @@
         <v>66987272.200000003</v>
       </c>
       <c r="AB29">
-        <f>AVERAGE(
-    ABS(B29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(D29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(H29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(J29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(L29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(N29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(P29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(R29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(T29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(V29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(X29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)),
-    ABS(Z29-AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29))
-)
-/AVERAGE(B29,D29,H29,J29,L29,N29,P29,R29,T29,V29,X29,Z29)</f>
+        <f t="shared" si="0"/>
         <v>3.4125462690421971E-4</v>
       </c>
     </row>
@@ -3641,21 +4351,7 @@
         <v>95586794.200000003</v>
       </c>
       <c r="AB30">
-        <f>AVERAGE(
-    ABS(B30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(D30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(H30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(J30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(L30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(N30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(P30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(R30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(T30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(V30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(X30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)),
-    ABS(Z30-AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30))
-)
-/AVERAGE(B30,D30,H30,J30,L30,N30,P30,R30,T30,V30,X30,Z30)</f>
+        <f t="shared" si="0"/>
         <v>2.3377537413577242E-4</v>
       </c>
     </row>
@@ -3736,21 +4432,7 @@
         <v>95476234</v>
       </c>
       <c r="AB31">
-        <f>AVERAGE(
-    ABS(B31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(D31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(H31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(J31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(L31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(N31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(P31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(R31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(T31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(V31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(X31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)),
-    ABS(Z31-AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31))
-)
-/AVERAGE(B31,D31,H31,J31,L31,N31,P31,R31,T31,V31,X31,Z31)</f>
+        <f t="shared" si="0"/>
         <v>2.5954854248945756E-4</v>
       </c>
     </row>
@@ -3831,38 +4513,24 @@
         <v>95543043.299999997</v>
       </c>
       <c r="AB32">
-        <f>AVERAGE(
-    ABS(B32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(D32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(H32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(J32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(L32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(N32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(P32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(R32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(T32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(V32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(X32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)),
-    ABS(Z32-AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32))
-)
-/AVERAGE(B32,D32,H32,J32,L32,N32,P32,R32,T32,V32,X32,Z32)</f>
+        <f t="shared" si="0"/>
         <v>2.515351266947099E-4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3879,6 +4547,7 @@
     <col min="3" max="3" width="17.5546875" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
@@ -3914,88 +4583,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="13" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="14" t="s">
+      <c r="M1" s="15"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="13" t="s">
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="13"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="6" t="s">
+      <c r="S1" s="15"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="6" t="s">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="7" t="s">
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="6" t="s">
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="16" t="s">
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-      <c r="AM1" s="16" t="s">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="11"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="19"/>
       <c r="C2" t="s">
         <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="F2" t="s">
@@ -4004,7 +4673,7 @@
       <c r="G2" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="I2" t="s">
@@ -4013,7 +4682,7 @@
       <c r="J2" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="L2" t="s">
@@ -4022,7 +4691,7 @@
       <c r="M2" t="s">
         <v>64</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="O2" t="s">
@@ -4031,7 +4700,7 @@
       <c r="P2" t="s">
         <v>64</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="R2" t="s">
@@ -4040,7 +4709,7 @@
       <c r="S2" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="U2" t="s">
@@ -4049,7 +4718,7 @@
       <c r="V2" t="s">
         <v>64</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="X2" t="s">
@@ -4058,7 +4727,7 @@
       <c r="Y2" t="s">
         <v>64</v>
       </c>
-      <c r="Z2" s="12" t="s">
+      <c r="Z2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AA2" t="s">
@@ -4067,7 +4736,7 @@
       <c r="AB2" t="s">
         <v>64</v>
       </c>
-      <c r="AC2" s="12" t="s">
+      <c r="AC2" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AD2" t="s">
@@ -4120,7 +4789,7 @@
       <c r="D3" s="5">
         <v>11.35</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="5">
         <f>C3*100/B3</f>
         <v>99.960376813875982</v>
       </c>
@@ -4130,7 +4799,7 @@
       <c r="G3">
         <v>11.86</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="5">
         <f>F3*100/B3</f>
         <v>99.973759479388065</v>
       </c>
@@ -4140,7 +4809,7 @@
       <c r="J3" t="s">
         <v>66</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <f>I3*100/C3</f>
         <v>99.950823272667449</v>
       </c>
@@ -4255,10 +4924,10 @@
       <c r="C4" s="5">
         <v>114049</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="10">
         <v>11.69</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="5">
         <f t="shared" ref="E4:E32" si="0">C4*100/B4</f>
         <v>99.961434969717686</v>
       </c>
@@ -4268,7 +4937,7 @@
       <c r="G4">
         <v>12.14</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="5">
         <f t="shared" ref="H4:H32" si="1">F4*100/B4</f>
         <v>99.958279649058227</v>
       </c>
@@ -4278,7 +4947,7 @@
       <c r="J4" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="5">
         <f t="shared" ref="K4:K32" si="2">I4*100/C4</f>
         <v>100.00491017019</v>
       </c>
@@ -4339,7 +5008,7 @@
         <v>11.49</v>
       </c>
       <c r="AC4" s="5">
-        <f t="shared" ref="AC4:AC33" si="8">AA4*100/B4</f>
+        <f t="shared" ref="AC4:AC32" si="8">AA4*100/B4</f>
         <v>99.889037890142248</v>
       </c>
       <c r="AD4" s="5">
@@ -4393,10 +5062,10 @@
       <c r="C5" s="5">
         <v>114228.2</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="10">
         <v>11.75</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5">
         <f t="shared" si="0"/>
         <v>99.967794162691987</v>
       </c>
@@ -4406,7 +5075,7 @@
       <c r="G5">
         <v>13.14</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="5">
         <f t="shared" si="1"/>
         <v>99.97155734476874</v>
       </c>
@@ -4416,7 +5085,7 @@
       <c r="J5" t="s">
         <v>68</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="5">
         <f t="shared" si="2"/>
         <v>100.01365687282124</v>
       </c>
@@ -4531,10 +5200,10 @@
       <c r="C6" s="5">
         <v>114207.8</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="10">
         <v>11.7</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="5">
         <f t="shared" si="0"/>
         <v>99.895737664768603</v>
       </c>
@@ -4544,7 +5213,7 @@
       <c r="G6">
         <v>12.56</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
         <v>99.943145538674159</v>
       </c>
@@ -4554,7 +5223,7 @@
       <c r="J6" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="5">
         <f t="shared" si="2"/>
         <v>100.02512963212671</v>
       </c>
@@ -4669,10 +5338,10 @@
       <c r="C7" s="5">
         <v>114176.7</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="10">
         <v>11.87</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="5">
         <f t="shared" si="0"/>
         <v>99.954214779084126</v>
       </c>
@@ -4682,7 +5351,7 @@
       <c r="G7">
         <v>12.9</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="5">
         <f t="shared" si="1"/>
         <v>99.980827985887998</v>
       </c>
@@ -4692,7 +5361,7 @@
       <c r="J7" t="s">
         <v>70</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="5">
         <f t="shared" si="2"/>
         <v>100.01462645180672</v>
       </c>
@@ -4807,10 +5476,10 @@
       <c r="C8" s="5">
         <v>114143.4</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="10">
         <v>11.76</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="5">
         <f t="shared" si="0"/>
         <v>99.938186211847935</v>
       </c>
@@ -4820,7 +5489,7 @@
       <c r="G8">
         <v>12.04</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="5">
         <f t="shared" si="1"/>
         <v>99.978724149403746</v>
       </c>
@@ -4830,7 +5499,7 @@
       <c r="J8" t="s">
         <v>71</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="5">
         <f t="shared" si="2"/>
         <v>100.00166457280929</v>
       </c>
@@ -4945,10 +5614,10 @@
       <c r="C9" s="5">
         <v>114178.1</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="10">
         <v>11.67</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="5">
         <f t="shared" si="0"/>
         <v>99.966817258527698</v>
       </c>
@@ -4958,7 +5627,7 @@
       <c r="G9">
         <v>12.39</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>99.962789801779081</v>
       </c>
@@ -4968,7 +5637,7 @@
       <c r="J9" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="5">
         <f t="shared" si="2"/>
         <v>99.973374929167676</v>
       </c>
@@ -5083,10 +5752,10 @@
       <c r="C10" s="5">
         <v>114286.9</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="10">
         <v>11.74</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="5">
         <f t="shared" si="0"/>
         <v>99.95793064241046</v>
       </c>
@@ -5096,7 +5765,7 @@
       <c r="G10">
         <v>11.82</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="5">
         <f t="shared" si="1"/>
         <v>99.981108147111556</v>
       </c>
@@ -5106,7 +5775,7 @@
       <c r="J10" t="s">
         <v>73</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="5">
         <f t="shared" si="2"/>
         <v>100.01881230482235</v>
       </c>
@@ -5221,10 +5890,10 @@
       <c r="C11" s="5">
         <v>114400.6</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="10">
         <v>11.61</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="5">
         <f t="shared" si="0"/>
         <v>99.993531920844703</v>
       </c>
@@ -5234,7 +5903,7 @@
       <c r="G11">
         <v>12.8</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="5">
         <f t="shared" si="1"/>
         <v>99.981994266135231</v>
       </c>
@@ -5244,7 +5913,7 @@
       <c r="J11" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="5">
         <f t="shared" si="2"/>
         <v>99.980769331629375</v>
       </c>
@@ -5359,10 +6028,10 @@
       <c r="C12" s="5">
         <v>114256.5</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="10">
         <v>11.77</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="5">
         <f t="shared" si="0"/>
         <v>99.91910729433576</v>
       </c>
@@ -5372,7 +6041,7 @@
       <c r="G12">
         <v>12.14</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="5">
         <f t="shared" si="1"/>
         <v>99.948840829390718</v>
       </c>
@@ -5382,7 +6051,7 @@
       <c r="J12" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="5">
         <f t="shared" si="2"/>
         <v>100.01627916136063</v>
       </c>
@@ -5497,10 +6166,10 @@
       <c r="C13" s="5">
         <v>11290114.300000001</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="10">
         <v>23.26</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <f t="shared" si="0"/>
         <v>100.02957709092482</v>
       </c>
@@ -5510,7 +6179,7 @@
       <c r="G13">
         <v>21.9</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <f t="shared" si="1"/>
         <v>100.02218392568436</v>
       </c>
@@ -5520,7 +6189,7 @@
       <c r="J13" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="5">
         <f t="shared" si="2"/>
         <v>99.993630711072598</v>
       </c>
@@ -5638,7 +6307,7 @@
       <c r="D14" s="5">
         <v>23.67</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="5">
         <f t="shared" si="0"/>
         <v>99.968509080873631</v>
       </c>
@@ -5648,7 +6317,7 @@
       <c r="G14">
         <v>22.25</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="5">
         <f t="shared" si="1"/>
         <v>99.983268965715141</v>
       </c>
@@ -5658,7 +6327,7 @@
       <c r="J14" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="20">
+      <c r="K14" s="5">
         <f t="shared" si="2"/>
         <v>100.01536237340483</v>
       </c>
@@ -5776,7 +6445,7 @@
       <c r="D15" s="5">
         <v>23.33</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="5">
         <f t="shared" si="0"/>
         <v>100.01132010708893</v>
       </c>
@@ -5786,7 +6455,7 @@
       <c r="G15">
         <v>22.11</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="5">
         <f t="shared" si="1"/>
         <v>100.0233897517387</v>
       </c>
@@ -5796,7 +6465,7 @@
       <c r="J15" t="s">
         <v>78</v>
       </c>
-      <c r="K15" s="20">
+      <c r="K15" s="5">
         <f t="shared" si="2"/>
         <v>100.01548668254655</v>
       </c>
@@ -5914,7 +6583,7 @@
       <c r="D16" s="5">
         <v>23.63</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="5">
         <f>C16*100/B16</f>
         <v>100.01239317733008</v>
       </c>
@@ -5924,7 +6593,7 @@
       <c r="G16">
         <v>21.96</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <f t="shared" si="1"/>
         <v>100.02445204366174</v>
       </c>
@@ -5934,7 +6603,7 @@
       <c r="J16" t="s">
         <v>79</v>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="5">
         <f t="shared" si="2"/>
         <v>99.998610090987626</v>
       </c>
@@ -6052,7 +6721,7 @@
       <c r="D17" s="5">
         <v>23.34</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="5">
         <f t="shared" si="0"/>
         <v>100.00700487721105</v>
       </c>
@@ -6062,7 +6731,7 @@
       <c r="G17">
         <v>22.08</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="5">
         <f t="shared" si="1"/>
         <v>100.00877650121743</v>
       </c>
@@ -6072,7 +6741,7 @@
       <c r="J17" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="20">
+      <c r="K17" s="5">
         <f t="shared" si="2"/>
         <v>99.994686296912178</v>
       </c>
@@ -6190,7 +6859,7 @@
       <c r="D18" s="5">
         <v>23.16</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="5">
         <f t="shared" si="0"/>
         <v>100.02320959022396</v>
       </c>
@@ -6200,7 +6869,7 @@
       <c r="G18">
         <v>22.27</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <f t="shared" si="1"/>
         <v>100.02042532593605</v>
       </c>
@@ -6210,7 +6879,7 @@
       <c r="J18" t="s">
         <v>81</v>
       </c>
-      <c r="K18" s="20">
+      <c r="K18" s="5">
         <f t="shared" si="2"/>
         <v>99.998915128095547</v>
       </c>
@@ -6328,7 +6997,7 @@
       <c r="D19" s="5">
         <v>22.94</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="5">
         <f t="shared" si="0"/>
         <v>100.06420302014538</v>
       </c>
@@ -6338,7 +7007,7 @@
       <c r="G19">
         <v>22.58</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="5">
         <f t="shared" si="1"/>
         <v>100.05773192586456</v>
       </c>
@@ -6348,7 +7017,7 @@
       <c r="J19" t="s">
         <v>82</v>
       </c>
-      <c r="K19" s="20">
+      <c r="K19" s="5">
         <f t="shared" si="2"/>
         <v>99.98723744036613</v>
       </c>
@@ -6466,7 +7135,7 @@
       <c r="D20" s="5">
         <v>22.97</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="5">
         <f t="shared" si="0"/>
         <v>100.0765308784086</v>
       </c>
@@ -6476,7 +7145,7 @@
       <c r="G20">
         <v>22.51</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="5">
         <f t="shared" si="1"/>
         <v>100.09300020885748</v>
       </c>
@@ -6486,7 +7155,7 @@
       <c r="J20" t="s">
         <v>83</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="5">
         <f t="shared" si="2"/>
         <v>100.00873774525033</v>
       </c>
@@ -6604,7 +7273,7 @@
       <c r="D21" s="5">
         <v>23.15</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="5">
         <f t="shared" si="0"/>
         <v>100.05733542435091</v>
       </c>
@@ -6614,7 +7283,7 @@
       <c r="G21">
         <v>22.36</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="5">
         <f t="shared" si="1"/>
         <v>100.03806788350006</v>
       </c>
@@ -6624,7 +7293,7 @@
       <c r="J21" t="s">
         <v>84</v>
       </c>
-      <c r="K21" s="20">
+      <c r="K21" s="5">
         <f t="shared" si="2"/>
         <v>99.984721616646851</v>
       </c>
@@ -6742,7 +7411,7 @@
       <c r="D22" s="5">
         <v>23.28</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="5">
         <f t="shared" si="0"/>
         <v>99.988950310446398</v>
       </c>
@@ -6752,7 +7421,7 @@
       <c r="G22">
         <v>22.22</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="5">
         <f t="shared" si="1"/>
         <v>100.01082363699638</v>
       </c>
@@ -6762,7 +7431,7 @@
       <c r="J22" t="s">
         <v>85</v>
       </c>
-      <c r="K22" s="20">
+      <c r="K22" s="5">
         <f t="shared" si="2"/>
         <v>100.00865038467323</v>
       </c>
@@ -6871,7 +7540,7 @@
       <c r="A23" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="7">
         <v>24905330</v>
       </c>
       <c r="C23" s="5">
@@ -6880,7 +7549,7 @@
       <c r="D23" s="5">
         <v>34.020000000000003</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="5">
         <f t="shared" si="0"/>
         <v>99.985366987709057</v>
       </c>
@@ -6890,17 +7559,17 @@
       <c r="G23">
         <v>34.94</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="5">
         <f t="shared" si="1"/>
         <v>99.986143528313022</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23">
         <v>24904061.699999999</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" t="s">
         <v>86</v>
       </c>
-      <c r="K23" s="21">
+      <c r="K23" s="5">
         <f t="shared" si="2"/>
         <v>100.00954192434266</v>
       </c>
@@ -7009,7 +7678,7 @@
       <c r="A24" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="7">
         <v>24900424</v>
       </c>
       <c r="C24" s="5">
@@ -7018,7 +7687,7 @@
       <c r="D24" s="5">
         <v>33.909999999999997</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="5">
         <f t="shared" si="0"/>
         <v>99.977828088389174</v>
       </c>
@@ -7028,17 +7697,17 @@
       <c r="G24">
         <v>34.840000000000003</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="5">
         <f t="shared" si="1"/>
         <v>100.00286019226019</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24">
         <v>24899345.899999999</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" t="s">
         <v>87</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K24" s="5">
         <f t="shared" si="2"/>
         <v>100.01784622330986</v>
       </c>
@@ -7147,7 +7816,7 @@
       <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="7">
         <v>43465087</v>
       </c>
       <c r="C25" s="5">
@@ -7156,7 +7825,7 @@
       <c r="D25" s="5">
         <v>33.97</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="5">
         <f t="shared" si="0"/>
         <v>99.919641251379531</v>
       </c>
@@ -7166,17 +7835,17 @@
       <c r="G25">
         <v>35.21</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="5">
         <f t="shared" si="1"/>
         <v>99.915091852916348</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25">
         <v>43428610.100000001</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J25" t="s">
         <v>88</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="5">
         <f t="shared" si="2"/>
         <v>99.996433584320982</v>
       </c>
@@ -7285,7 +7954,7 @@
       <c r="A26" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="7">
         <v>43437261</v>
       </c>
       <c r="C26" s="5">
@@ -7294,7 +7963,7 @@
       <c r="D26" s="5">
         <v>34.15</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="5">
         <f t="shared" si="0"/>
         <v>100.03388381233339</v>
       </c>
@@ -7304,17 +7973,17 @@
       <c r="G26">
         <v>35.119999999999997</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="5">
         <f t="shared" si="1"/>
         <v>100.05872239504235</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26">
         <v>43450682.5</v>
       </c>
       <c r="J26" t="s">
         <v>89</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K26" s="5">
         <f t="shared" si="2"/>
         <v>99.997015786107156</v>
       </c>
@@ -7423,7 +8092,7 @@
       <c r="A27" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="7">
         <v>43476251</v>
       </c>
       <c r="C27" s="5">
@@ -7432,7 +8101,7 @@
       <c r="D27" s="5">
         <v>34.4</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="5">
         <f t="shared" si="0"/>
         <v>99.925668613883019</v>
       </c>
@@ -7442,17 +8111,17 @@
       <c r="G27">
         <v>35.36</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="5">
         <f t="shared" si="1"/>
         <v>99.973120037419974</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27">
         <v>43455542</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="J27" t="s">
         <v>90</v>
       </c>
-      <c r="K27" s="21">
+      <c r="K27" s="5">
         <f t="shared" si="2"/>
         <v>100.0267183443065</v>
       </c>
@@ -7561,7 +8230,7 @@
       <c r="A28" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="8">
         <v>67021888</v>
       </c>
       <c r="C28" s="5">
@@ -7570,7 +8239,7 @@
       <c r="D28" s="5">
         <v>34.57</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="5">
         <f t="shared" si="0"/>
         <v>99.95227693376826</v>
       </c>
@@ -7580,17 +8249,17 @@
       <c r="G28">
         <v>35.83</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="5">
         <f t="shared" si="1"/>
         <v>99.962051352537244</v>
       </c>
-      <c r="I28" s="22">
+      <c r="I28">
         <v>66994799.799999997</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K28" s="5">
         <f t="shared" si="2"/>
         <v>100.00730960902077</v>
       </c>
@@ -7699,7 +8368,7 @@
       <c r="A29" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="7">
         <v>66979606</v>
       </c>
       <c r="C29" s="5">
@@ -7708,7 +8377,7 @@
       <c r="D29" s="5">
         <v>34.75</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="5">
         <f t="shared" si="0"/>
         <v>100.04523018543884</v>
       </c>
@@ -7718,17 +8387,17 @@
       <c r="G29">
         <v>35.729999999999997</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="5">
         <f t="shared" si="1"/>
         <v>100.05267379446812</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29">
         <v>67016469</v>
       </c>
       <c r="J29" t="s">
         <v>92</v>
       </c>
-      <c r="K29" s="21">
+      <c r="K29" s="5">
         <f t="shared" si="2"/>
         <v>100.00980153664158</v>
       </c>
@@ -7837,7 +8506,7 @@
       <c r="A30" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="8">
         <v>95556435</v>
       </c>
       <c r="C30" s="5">
@@ -7846,7 +8515,7 @@
       <c r="D30" s="5">
         <v>34.799999999999997</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="5">
         <f t="shared" si="0"/>
         <v>100.06770742336714</v>
       </c>
@@ -7856,17 +8525,17 @@
       <c r="G30">
         <v>35.979999999999997</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="5">
         <f t="shared" si="1"/>
         <v>100.06736772881911</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30">
         <v>95626473.5</v>
       </c>
-      <c r="J30" s="20" t="s">
+      <c r="J30" t="s">
         <v>93</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K30" s="5">
         <f t="shared" si="2"/>
         <v>100.005584225775</v>
       </c>
@@ -7975,7 +8644,7 @@
       <c r="A31" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="7">
         <v>95629207</v>
       </c>
       <c r="C31" s="5">
@@ -7984,7 +8653,7 @@
       <c r="D31" s="5">
         <v>34.97</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="5">
         <f t="shared" si="0"/>
         <v>99.877257478460535</v>
       </c>
@@ -7994,17 +8663,17 @@
       <c r="G31">
         <v>35.94</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="5">
         <f t="shared" si="1"/>
         <v>99.881033312343575</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31">
         <v>95516151.299999997</v>
       </c>
-      <c r="J31" s="20" t="s">
+      <c r="J31" t="s">
         <v>94</v>
       </c>
-      <c r="K31" s="21">
+      <c r="K31" s="5">
         <f t="shared" si="2"/>
         <v>100.00452509394039</v>
       </c>
@@ -8113,7 +8782,7 @@
       <c r="A32" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="9">
         <v>95643586</v>
       </c>
       <c r="C32" s="5">
@@ -8122,7 +8791,7 @@
       <c r="D32">
         <v>34.950000000000003</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="5">
         <f t="shared" si="0"/>
         <v>99.921187919491018</v>
       </c>
@@ -8132,17 +8801,17 @@
       <c r="G32">
         <v>36.11</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="5">
         <f t="shared" si="1"/>
         <v>99.926408551849988</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32">
         <v>95573812.400000006</v>
       </c>
-      <c r="J32" s="20" t="s">
+      <c r="J32" t="s">
         <v>95</v>
       </c>
-      <c r="K32" s="21">
+      <c r="K32" s="5">
         <f t="shared" si="2"/>
         <v>100.00586502578457</v>
       </c>
@@ -8252,22 +8921,32 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02382364-23F3-4508-A7B8-9D41EA4AC020}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExperimentoCompleto.xlsx
+++ b/ExperimentoCompleto.xlsx
@@ -8,121 +8,150 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E07583D-6AF2-4BF7-AF0A-CD6086101DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8590519B-5A11-42E2-BF98-C4FCC05EAB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
     <sheet name="Planilha2" sheetId="5" r:id="rId3"/>
+    <sheet name="Planilha3" sheetId="6" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Planilha1!$H$35</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.100" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.101" hidden="1">Planilha1!$U$1</definedName>
-    <definedName name="_xlchart.v1.102" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.103" hidden="1">Planilha1!$X$1</definedName>
-    <definedName name="_xlchart.v1.104" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Planilha1!$F$1</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Planilha1!$I$1</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Planilha1!$K$3:$K$31</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.100" hidden="1">[1]Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.101" hidden="1">[1]Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.102" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.103" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.104" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.105" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.106" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.107" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.108" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.109" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.110" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.111" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.112" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.113" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.114" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.115" hidden="1">Planilha3!$K:$K</definedName>
+    <definedName name="_xlchart.v1.116" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.117" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.118" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.119" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.120" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.121" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.122" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.123" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.124" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.125" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.126" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.127" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.128" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.129" hidden="1">Planilha3!$K:$K</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">Planilha1!$AA$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">Planilha1!$AD$1</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">Planilha1!$AG$1</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">Planilha1!$AJ$1</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">Planilha1!$AM$1</definedName>
     <definedName name="_xlchart.v1.48" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
     <definedName name="_xlchart.v1.49" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Planilha1!$E$3:$E$32</definedName>
     <definedName name="_xlchart.v1.50" hidden="1">Planilha1!$E$3:$E$32</definedName>
     <definedName name="_xlchart.v1.51" hidden="1">Planilha1!$F$1</definedName>
     <definedName name="_xlchart.v1.52" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">Planilha1!$I$1</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">Planilha1!$K$3:$K$31</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.53" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.54" hidden="1">Planilha1!$L$1</definedName>
+    <definedName name="_xlchart.v1.55" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.56" hidden="1">Planilha1!$O$1</definedName>
     <definedName name="_xlchart.v1.57" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.58" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">Planilha1!$F$1</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">Planilha1!$I$1</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">Planilha1!$K$3:$K$31</definedName>
-    <definedName name="_xlchart.v1.72" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.73" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.74" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.75" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.76" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.77" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.78" hidden="1">Planilha1!$AA$1</definedName>
-    <definedName name="_xlchart.v1.79" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.80" hidden="1">Planilha1!$AD$1</definedName>
-    <definedName name="_xlchart.v1.81" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.82" hidden="1">Planilha1!$AG$1</definedName>
-    <definedName name="_xlchart.v1.83" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.84" hidden="1">Planilha1!$AJ$1</definedName>
-    <definedName name="_xlchart.v1.85" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.86" hidden="1">Planilha1!$AM$1</definedName>
-    <definedName name="_xlchart.v1.87" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.88" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.89" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.90" hidden="1">Planilha1!$F$1</definedName>
-    <definedName name="_xlchart.v1.91" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.92" hidden="1">Planilha1!$I$1</definedName>
-    <definedName name="_xlchart.v1.93" hidden="1">Planilha1!$K$3:$K$31</definedName>
-    <definedName name="_xlchart.v1.94" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.95" hidden="1">Planilha1!$L$1</definedName>
-    <definedName name="_xlchart.v1.96" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.97" hidden="1">Planilha1!$O$1</definedName>
-    <definedName name="_xlchart.v1.98" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.99" hidden="1">Planilha1!$R$1</definedName>
+    <definedName name="_xlchart.v1.58" hidden="1">Planilha1!$R$1</definedName>
+    <definedName name="_xlchart.v1.59" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.60" hidden="1">Planilha1!$U$1</definedName>
+    <definedName name="_xlchart.v1.61" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.62" hidden="1">Planilha1!$X$1</definedName>
+    <definedName name="_xlchart.v1.63" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.64" hidden="1">Planilha1!$AA$1</definedName>
+    <definedName name="_xlchart.v1.65" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.66" hidden="1">Planilha1!$AD$1</definedName>
+    <definedName name="_xlchart.v1.67" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.68" hidden="1">Planilha1!$AG$1</definedName>
+    <definedName name="_xlchart.v1.69" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.70" hidden="1">Planilha1!$AJ$1</definedName>
+    <definedName name="_xlchart.v1.71" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.72" hidden="1">Planilha1!$AM$1</definedName>
+    <definedName name="_xlchart.v1.73" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.74" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.75" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.76" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.77" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.78" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.79" hidden="1">Planilha1!$L$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.80" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.81" hidden="1">Planilha1!$O$1</definedName>
+    <definedName name="_xlchart.v1.82" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.83" hidden="1">Planilha1!$R$1</definedName>
+    <definedName name="_xlchart.v1.84" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.85" hidden="1">Planilha1!$U$1</definedName>
+    <definedName name="_xlchart.v1.86" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.87" hidden="1">Planilha1!$X$1</definedName>
+    <definedName name="_xlchart.v1.88" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.89" hidden="1">[1]Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.90" hidden="1">[1]Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.91" hidden="1">[1]Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.92" hidden="1">[1]Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.93" hidden="1">[1]Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.94" hidden="1">[1]Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.95" hidden="1">[1]Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.96" hidden="1">[1]Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.97" hidden="1">[1]Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.98" hidden="1">[1]Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.99" hidden="1">[1]Planilha1!$T$3:$T$32</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -437,7 +466,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -581,7 +610,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -594,20 +623,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -632,67 +661,67 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.89</cx:f>
+        <cx:f>_xlchart.v1.75</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.91</cx:f>
+        <cx:f>_xlchart.v1.77</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.96</cx:f>
+        <cx:f>_xlchart.v1.80</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.98</cx:f>
+        <cx:f>_xlchart.v1.82</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.100</cx:f>
+        <cx:f>_xlchart.v1.84</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.102</cx:f>
+        <cx:f>_xlchart.v1.86</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="6">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.104</cx:f>
+        <cx:f>_xlchart.v1.88</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="7">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.79</cx:f>
+        <cx:f>_xlchart.v1.65</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="8">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.81</cx:f>
+        <cx:f>_xlchart.v1.67</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="9">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.83</cx:f>
+        <cx:f>_xlchart.v1.69</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="10">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.85</cx:f>
+        <cx:f>_xlchart.v1.71</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="11">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.87</cx:f>
+        <cx:f>_xlchart.v1.73</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="12">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.94</cx:f>
+        <cx:f>_xlchart.v1.78</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -730,7 +759,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F027B10E-9D4A-42C2-A360-996EFF7CDC29}" formatIdx="0">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.88</cx:f>
+              <cx:f>_xlchart.v1.74</cx:f>
               <cx:v>Padrão</cx:v>
             </cx:txData>
           </cx:tx>
@@ -743,7 +772,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{25922C5E-E129-4246-B9EF-39947B99D9C5}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.90</cx:f>
+              <cx:f>_xlchart.v1.76</cx:f>
               <cx:v>Irace Geral</cx:v>
             </cx:txData>
           </cx:tx>
@@ -756,7 +785,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{8DA59056-C9D5-427C-8AA4-463B2127A648}" formatIdx="2">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.95</cx:f>
+              <cx:f>_xlchart.v1.79</cx:f>
               <cx:v>Configuracao 2 16 7 1656 63656 2,09 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -769,7 +798,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{16C9E66D-30A4-4E13-91E8-ED12B2DB9FDE}" formatIdx="3">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.97</cx:f>
+              <cx:f>_xlchart.v1.81</cx:f>
               <cx:v>Configuracao 2 18 6 2542 73603 2,03 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -782,7 +811,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F2D5FD8D-045E-43AE-B8C5-E64209EAA869}" formatIdx="4">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.99</cx:f>
+              <cx:f>_xlchart.v1.83</cx:f>
               <cx:v>Configuracao  2 10 16 1644 24767 2,96 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -795,7 +824,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{17BC3A71-22EB-47CC-B52A-284F6EFA9E05}" formatIdx="5">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.101</cx:f>
+              <cx:f>_xlchart.v1.85</cx:f>
               <cx:v>Configuração  2 14 13 2405 43525 0,87 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -808,7 +837,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5F522F99-7A97-4E23-9D13-87A6755777B4}" formatIdx="6">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.103</cx:f>
+              <cx:f>_xlchart.v1.87</cx:f>
               <cx:v>Configuração  2 14 19 1795 66816 2,77 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -821,7 +850,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{971181E6-C471-4560-9CA5-01A74C68C9D8}" formatIdx="7">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.78</cx:f>
+              <cx:f>_xlchart.v1.64</cx:f>
               <cx:v>Configuração  2 20 20 1079 55559 1,08 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -834,7 +863,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{CC135088-7A79-4E02-B37B-A1F392DFA551}" formatIdx="8">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.80</cx:f>
+              <cx:f>_xlchart.v1.66</cx:f>
               <cx:v>Configuração  2 18 13 2520 13214 0,67 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -847,7 +876,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{3B130AD7-A71E-4A58-8854-C53F8AA3DE5E}" formatIdx="9">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.82</cx:f>
+              <cx:f>_xlchart.v1.68</cx:f>
               <cx:v>Configuração  2 11 16 1797 24360 2,34 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -860,7 +889,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6D41FE1A-A51D-419E-8C75-BC8EA43C68DD}" formatIdx="10">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.84</cx:f>
+              <cx:f>_xlchart.v1.70</cx:f>
               <cx:v>Configuração  2 11 17 2326 31236 1,35 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -873,7 +902,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{1324BC5E-E88F-457C-8C14-B953E60EF5EE}" formatIdx="11">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.86</cx:f>
+              <cx:f>_xlchart.v1.72</cx:f>
               <cx:v>Configuração  2 19 6 2851 43903 1,75 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -886,6 +915,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{CF456752-E8AB-4A6C-A2A8-C4D80D7BE8AF}" formatIdx="12">
           <cx:tx>
             <cx:txData>
+              <cx:f/>
               <cx:v>Irace separado</cx:v>
             </cx:txData>
           </cx:tx>
@@ -962,7 +992,252 @@
 </cx:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.107</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.108</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.109</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.110</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="4">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.111</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="5">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.112</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="6">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.113</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="7">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.114</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="8">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.102</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="9">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.103</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="10">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.104</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="11">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.105</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="12">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.106</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{CCC66ADE-7979-48B9-80FE-02C2A5D0741A}">
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{DE12E5D0-3815-4D8A-8DA6-FD1F5C6E976E}">
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{7E9AA417-B139-4B19-9688-5CB25A143A26}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.115</cx:f>
+              <cx:v/>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{19E8D587-E02B-4BB9-83D6-902B45F2F036}">
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{D65D489C-2013-4BA9-8126-457D63379F9B}">
+          <cx:dataId val="4"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{EC2AB0F9-60BE-40C0-9ACD-6518155B5726}">
+          <cx:dataId val="5"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{D1DE3512-34E7-496F-B4ED-A0D0B3C72EC1}">
+          <cx:dataId val="6"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{946ABE6C-7721-466D-9961-C55B566ACF1B}">
+          <cx:dataId val="7"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{B1FB5F0F-FA22-48CA-BC16-AC23172773E4}">
+          <cx:dataId val="8"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{CBE7198A-C2D2-489E-9260-2A2D343502BC}">
+          <cx:dataId val="9"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{D82772A9-96FE-414A-A0DF-7707B59706A8}">
+          <cx:dataId val="10"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{46544867-521D-41D3-A184-BEE63DF4366C}">
+          <cx:dataId val="11"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{D0F610E0-E89A-469A-8C52-81F833143880}">
+          <cx:dataId val="12"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling max="100.40000000000001" min="99.299999999999997"/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0">
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:sysClr>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </cx:txPr>
+    </cx:legend>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1517,29 +1792,544 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>487680</xdr:colOff>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="2" name="Gráfico 1">
+            <xdr:cNvPr id="3" name="Gráfico 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E89937F0-9DA7-4960-A9AE-71155BA67E94}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053C686B-2F11-4934-AD58-4076161C13B1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1566,7 +2356,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="487680" y="144780"/>
+              <a:off x="22860" y="0"/>
               <a:ext cx="9845040" cy="4526280"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1598,6 +2388,1342 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Gráfico 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9818F91-B9B8-4A3D-87A1-BD4915CD4C48}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="10180320" cy="4526280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Planilha1"/>
+      <sheetName val="Planilha2"/>
+      <sheetName val="Planilha3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="E3">
+            <v>99.960376813875982</v>
+          </cell>
+          <cell r="H3">
+            <v>99.913143876774512</v>
+          </cell>
+          <cell r="K3">
+            <v>99.947235646652089</v>
+          </cell>
+          <cell r="N3">
+            <v>99.321682542181634</v>
+          </cell>
+          <cell r="Q3">
+            <v>99.497668967085644</v>
+          </cell>
+          <cell r="T3">
+            <v>99.244710348386647</v>
+          </cell>
+          <cell r="W3">
+            <v>99.244885285190719</v>
+          </cell>
+          <cell r="Z3">
+            <v>99.569830398768445</v>
+          </cell>
+          <cell r="AC3">
+            <v>99.633070053443191</v>
+          </cell>
+          <cell r="AF3">
+            <v>99.895562727964517</v>
+          </cell>
+          <cell r="AI3">
+            <v>99.138173834702215</v>
+          </cell>
+          <cell r="AL3">
+            <v>99.153918147069376</v>
+          </cell>
+          <cell r="AO3">
+            <v>99.502829602805988</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4">
+            <v>99.961434969717686</v>
+          </cell>
+          <cell r="H4">
+            <v>99.952407246719787</v>
+          </cell>
+          <cell r="K4">
+            <v>99.9882506641882</v>
+          </cell>
+          <cell r="N4">
+            <v>99.449308897127779</v>
+          </cell>
+          <cell r="Q4">
+            <v>99.533363133584004</v>
+          </cell>
+          <cell r="T4">
+            <v>99.455093651670126</v>
+          </cell>
+          <cell r="W4">
+            <v>99.321080171439093</v>
+          </cell>
+          <cell r="Z4">
+            <v>99.649408815615331</v>
+          </cell>
+          <cell r="AC4">
+            <v>99.621975055437233</v>
+          </cell>
+          <cell r="AF4">
+            <v>99.82268850849745</v>
+          </cell>
+          <cell r="AI4">
+            <v>99.209241583620383</v>
+          </cell>
+          <cell r="AL4">
+            <v>99.324761378875124</v>
+          </cell>
+          <cell r="AO4">
+            <v>99.636086350608707</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5">
+            <v>99.967794162691987</v>
+          </cell>
+          <cell r="H5">
+            <v>99.974270336498492</v>
+          </cell>
+          <cell r="K5">
+            <v>100.00026263216964</v>
+          </cell>
+          <cell r="N5">
+            <v>99.55681967356584</v>
+          </cell>
+          <cell r="Q5">
+            <v>99.657812978602365</v>
+          </cell>
+          <cell r="T5">
+            <v>99.389751892530526</v>
+          </cell>
+          <cell r="W5">
+            <v>99.313000481337241</v>
+          </cell>
+          <cell r="Z5">
+            <v>99.621406379906361</v>
+          </cell>
+          <cell r="AC5">
+            <v>99.714785804927146</v>
+          </cell>
+          <cell r="AF5">
+            <v>99.831882028617684</v>
+          </cell>
+          <cell r="AI5">
+            <v>99.168599308624692</v>
+          </cell>
+          <cell r="AL5">
+            <v>99.29348444405548</v>
+          </cell>
+          <cell r="AO5">
+            <v>99.667264691725379</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6">
+            <v>99.895737664768603</v>
+          </cell>
+          <cell r="H6">
+            <v>99.91296893997044</v>
+          </cell>
+          <cell r="K6">
+            <v>99.969529226550193</v>
+          </cell>
+          <cell r="N6">
+            <v>99.201238552572889</v>
+          </cell>
+          <cell r="Q6">
+            <v>99.519973409605782</v>
+          </cell>
+          <cell r="T6">
+            <v>99.239987054676504</v>
+          </cell>
+          <cell r="W6">
+            <v>99.211559824013577</v>
+          </cell>
+          <cell r="Z6">
+            <v>99.544901904187114</v>
+          </cell>
+          <cell r="AC6">
+            <v>99.576915339333667</v>
+          </cell>
+          <cell r="AF6">
+            <v>99.88646601415239</v>
+          </cell>
+          <cell r="AI6">
+            <v>98.987028435977507</v>
+          </cell>
+          <cell r="AL6">
+            <v>99.238937433852016</v>
+          </cell>
+          <cell r="AO6">
+            <v>99.588898510413117</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7">
+            <v>99.954214779084126</v>
+          </cell>
+          <cell r="H7">
+            <v>99.990983025326315</v>
+          </cell>
+          <cell r="K7">
+            <v>100.01208652903789</v>
+          </cell>
+          <cell r="N7">
+            <v>99.584168643689438</v>
+          </cell>
+          <cell r="Q7">
+            <v>99.646674662301166</v>
+          </cell>
+          <cell r="T7">
+            <v>99.327841441315257</v>
+          </cell>
+          <cell r="W7">
+            <v>99.273476962942865</v>
+          </cell>
+          <cell r="Z7">
+            <v>99.651314464803164</v>
+          </cell>
+          <cell r="AC7">
+            <v>99.677927671607037</v>
+          </cell>
+          <cell r="AF7">
+            <v>99.869997986500806</v>
+          </cell>
+          <cell r="AI7">
+            <v>99.193637342531233</v>
+          </cell>
+          <cell r="AL7">
+            <v>99.240648171655181</v>
+          </cell>
+          <cell r="AO7">
+            <v>99.588020555200515</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8">
+            <v>99.938186211847935</v>
+          </cell>
+          <cell r="H8">
+            <v>99.948867914616429</v>
+          </cell>
+          <cell r="K8">
+            <v>99.982653399145292</v>
+          </cell>
+          <cell r="N8">
+            <v>99.387640744567221</v>
+          </cell>
+          <cell r="Q8">
+            <v>99.616772024445339</v>
+          </cell>
+          <cell r="T8">
+            <v>99.409792144570716</v>
+          </cell>
+          <cell r="W8">
+            <v>99.220585917663328</v>
+          </cell>
+          <cell r="Z8">
+            <v>99.613795156460682</v>
+          </cell>
+          <cell r="AC8">
+            <v>99.683138669515117</v>
+          </cell>
+          <cell r="AF8">
+            <v>99.8796119565027</v>
+          </cell>
+          <cell r="AI8">
+            <v>99.125851471798555</v>
+          </cell>
+          <cell r="AL8">
+            <v>99.292818743761714</v>
+          </cell>
+          <cell r="AO8">
+            <v>99.561174637084775</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9">
+            <v>99.966817258527698</v>
+          </cell>
+          <cell r="H9">
+            <v>99.966554598304967</v>
+          </cell>
+          <cell r="K9">
+            <v>99.973374929167676</v>
+          </cell>
+          <cell r="N9">
+            <v>99.394217972963503</v>
+          </cell>
+          <cell r="Q9">
+            <v>99.504797926735307</v>
+          </cell>
+          <cell r="T9">
+            <v>99.332930587658467</v>
+          </cell>
+          <cell r="W9">
+            <v>99.217797856692584</v>
+          </cell>
+          <cell r="Z9">
+            <v>99.636215591510819</v>
+          </cell>
+          <cell r="AC9">
+            <v>99.621243958814873</v>
+          </cell>
+          <cell r="AF9">
+            <v>99.868319675001757</v>
+          </cell>
+          <cell r="AI9">
+            <v>99.167717307557609</v>
+          </cell>
+          <cell r="AL9">
+            <v>99.174458919941159</v>
+          </cell>
+          <cell r="AO9">
+            <v>99.497005673460805</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10">
+            <v>99.95793064241046</v>
+          </cell>
+          <cell r="H10">
+            <v>99.954869462544281</v>
+          </cell>
+          <cell r="K10">
+            <v>100.01128738289341</v>
+          </cell>
+          <cell r="N10">
+            <v>99.448900161805227</v>
+          </cell>
+          <cell r="Q10">
+            <v>99.575807932828965</v>
+          </cell>
+          <cell r="T10">
+            <v>99.37062141951283</v>
+          </cell>
+          <cell r="W10">
+            <v>99.304237547557619</v>
+          </cell>
+          <cell r="Z10">
+            <v>99.621988017667377</v>
+          </cell>
+          <cell r="AC10">
+            <v>99.651900118074082</v>
+          </cell>
+          <cell r="AF10">
+            <v>99.900817772335685</v>
+          </cell>
+          <cell r="AI10">
+            <v>99.237416364192939</v>
+          </cell>
+          <cell r="AL10">
+            <v>99.286832553461323</v>
+          </cell>
+          <cell r="AO10">
+            <v>99.548694625442778</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11">
+            <v>99.993531920844703</v>
+          </cell>
+          <cell r="H11">
+            <v>99.973690651003423</v>
+          </cell>
+          <cell r="K11">
+            <v>99.994318211617767</v>
+          </cell>
+          <cell r="N11">
+            <v>99.364817145654143</v>
+          </cell>
+          <cell r="Q11">
+            <v>99.653345919865743</v>
+          </cell>
+          <cell r="T11">
+            <v>99.378277742815186</v>
+          </cell>
+          <cell r="W11">
+            <v>99.223917907838612</v>
+          </cell>
+          <cell r="Z11">
+            <v>99.650636319138528</v>
+          </cell>
+          <cell r="AC11">
+            <v>99.62939654569611</v>
+          </cell>
+          <cell r="AF11">
+            <v>99.885672330606255</v>
+          </cell>
+          <cell r="AI11">
+            <v>99.136948465142297</v>
+          </cell>
+          <cell r="AL11">
+            <v>99.305730368505692</v>
+          </cell>
+          <cell r="AO11">
+            <v>99.541553038249077</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12">
+            <v>99.91910729433576</v>
+          </cell>
+          <cell r="H12">
+            <v>99.936859963795044</v>
+          </cell>
+          <cell r="K12">
+            <v>99.99457361287979</v>
+          </cell>
+          <cell r="N12">
+            <v>99.365363929723912</v>
+          </cell>
+          <cell r="Q12">
+            <v>99.537993336190084</v>
+          </cell>
+          <cell r="T12">
+            <v>99.347873614985701</v>
+          </cell>
+          <cell r="W12">
+            <v>99.285695546091347</v>
+          </cell>
+          <cell r="Z12">
+            <v>99.605680854226975</v>
+          </cell>
+          <cell r="AC12">
+            <v>99.628418263386649</v>
+          </cell>
+          <cell r="AF12">
+            <v>99.826496077796918</v>
+          </cell>
+          <cell r="AI12">
+            <v>99.242669371835348</v>
+          </cell>
+          <cell r="AL12">
+            <v>99.279224129638209</v>
+          </cell>
+          <cell r="AO12">
+            <v>99.554521683617693</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13">
+            <v>100.02957709092482</v>
+          </cell>
+          <cell r="H13">
+            <v>100.01518352096294</v>
+          </cell>
+          <cell r="K13">
+            <v>99.979446266544883</v>
+          </cell>
+          <cell r="N13">
+            <v>99.514304882102735</v>
+          </cell>
+          <cell r="Q13">
+            <v>99.72745698151536</v>
+          </cell>
+          <cell r="T13">
+            <v>99.509547722042143</v>
+          </cell>
+          <cell r="W13">
+            <v>99.301232610623259</v>
+          </cell>
+          <cell r="Z13">
+            <v>99.749335151153886</v>
+          </cell>
+          <cell r="AC13">
+            <v>99.772372996504942</v>
+          </cell>
+          <cell r="AF13">
+            <v>99.883224580695142</v>
+          </cell>
+          <cell r="AI13">
+            <v>99.284637171854925</v>
+          </cell>
+          <cell r="AL13">
+            <v>99.488720339625772</v>
+          </cell>
+          <cell r="AO13">
+            <v>99.72654423194011</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14">
+            <v>99.968509080873631</v>
+          </cell>
+          <cell r="H14">
+            <v>99.95197794254014</v>
+          </cell>
+          <cell r="K14">
+            <v>100.01919065205071</v>
+          </cell>
+          <cell r="N14">
+            <v>99.546366118335925</v>
+          </cell>
+          <cell r="Q14">
+            <v>99.694302761681698</v>
+          </cell>
+          <cell r="T14">
+            <v>99.480794400858599</v>
+          </cell>
+          <cell r="W14">
+            <v>99.403957036452624</v>
+          </cell>
+          <cell r="Z14">
+            <v>99.729760247080961</v>
+          </cell>
+          <cell r="AC14">
+            <v>99.713292699927393</v>
+          </cell>
+          <cell r="AF14">
+            <v>99.837686081697484</v>
+          </cell>
+          <cell r="AI14">
+            <v>99.247215317432463</v>
+          </cell>
+          <cell r="AL14">
+            <v>99.474742345012444</v>
+          </cell>
+          <cell r="AO14">
+            <v>99.701314353521255</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15">
+            <v>100.01132010708893</v>
+          </cell>
+          <cell r="H15">
+            <v>100.00221717532024</v>
+          </cell>
+          <cell r="K15">
+            <v>100.00192011841635</v>
+          </cell>
+          <cell r="N15">
+            <v>99.575204635089264</v>
+          </cell>
+          <cell r="Q15">
+            <v>99.726964826285112</v>
+          </cell>
+          <cell r="T15">
+            <v>99.531221905624861</v>
+          </cell>
+          <cell r="W15">
+            <v>99.33850768701069</v>
+          </cell>
+          <cell r="Z15">
+            <v>99.804102549207002</v>
+          </cell>
+          <cell r="AC15">
+            <v>99.772658633815482</v>
+          </cell>
+          <cell r="AF15">
+            <v>99.900910673967459</v>
+          </cell>
+          <cell r="AI15">
+            <v>99.29305864812612</v>
+          </cell>
+          <cell r="AL15">
+            <v>99.476081392127867</v>
+          </cell>
+          <cell r="AO15">
+            <v>99.739438463178786</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>100.01239317733008</v>
+          </cell>
+          <cell r="H16">
+            <v>100.01217251965969</v>
+          </cell>
+          <cell r="K16">
+            <v>100.00544112148638</v>
+          </cell>
+          <cell r="N16">
+            <v>99.590472661726523</v>
+          </cell>
+          <cell r="Q16">
+            <v>99.720449870085289</v>
+          </cell>
+          <cell r="T16">
+            <v>99.525576611427368</v>
+          </cell>
+          <cell r="W16">
+            <v>99.386691978628065</v>
+          </cell>
+          <cell r="Z16">
+            <v>99.780554306713512</v>
+          </cell>
+          <cell r="AC16">
+            <v>99.784902831980816</v>
+          </cell>
+          <cell r="AF16">
+            <v>99.872284599252595</v>
+          </cell>
+          <cell r="AI16">
+            <v>99.343771978388276</v>
+          </cell>
+          <cell r="AL16">
+            <v>99.523660728376015</v>
+          </cell>
+          <cell r="AO16">
+            <v>99.751141321879658</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17">
+            <v>100.00700487721105</v>
+          </cell>
+          <cell r="H17">
+            <v>99.996816777712226</v>
+          </cell>
+          <cell r="K17">
+            <v>99.992597107835408</v>
+          </cell>
+          <cell r="N17">
+            <v>99.563697686389887</v>
+          </cell>
+          <cell r="Q17">
+            <v>99.740052928296279</v>
+          </cell>
+          <cell r="T17">
+            <v>99.598994548270397</v>
+          </cell>
+          <cell r="W17">
+            <v>99.28502927698743</v>
+          </cell>
+          <cell r="Z17">
+            <v>99.69133225009881</v>
+          </cell>
+          <cell r="AC17">
+            <v>99.807325332860032</v>
+          </cell>
+          <cell r="AF17">
+            <v>99.874319861655223</v>
+          </cell>
+          <cell r="AI17">
+            <v>99.293593409944663</v>
+          </cell>
+          <cell r="AL17">
+            <v>99.537604983527956</v>
+          </cell>
+          <cell r="AO17">
+            <v>99.71382912189398</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>100.02320959022396</v>
+          </cell>
+          <cell r="H18">
+            <v>100.02737437299531</v>
+          </cell>
+          <cell r="K18">
+            <v>99.996916889771512</v>
+          </cell>
+          <cell r="N18">
+            <v>99.585452338778452</v>
+          </cell>
+          <cell r="Q18">
+            <v>99.69848268855354</v>
+          </cell>
+          <cell r="T18">
+            <v>99.567717392653435</v>
+          </cell>
+          <cell r="W18">
+            <v>99.38526935713513</v>
+          </cell>
+          <cell r="Z18">
+            <v>99.770713007831688</v>
+          </cell>
+          <cell r="AC18">
+            <v>99.776613101982122</v>
+          </cell>
+          <cell r="AF18">
+            <v>99.896568207648698</v>
+          </cell>
+          <cell r="AI18">
+            <v>99.338634127140324</v>
+          </cell>
+          <cell r="AL18">
+            <v>99.528400719160416</v>
+          </cell>
+          <cell r="AO18">
+            <v>99.729952162357208</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>100.06420302014538</v>
+          </cell>
+          <cell r="H19">
+            <v>100.06211149567268</v>
+          </cell>
+          <cell r="K19">
+            <v>99.996902508085242</v>
+          </cell>
+          <cell r="N19">
+            <v>99.676254172301014</v>
+          </cell>
+          <cell r="Q19">
+            <v>99.767400495246761</v>
+          </cell>
+          <cell r="T19">
+            <v>99.684608569355603</v>
+          </cell>
+          <cell r="W19">
+            <v>99.443453182693929</v>
+          </cell>
+          <cell r="Z19">
+            <v>99.807445366180772</v>
+          </cell>
+          <cell r="AC19">
+            <v>99.852138039728771</v>
+          </cell>
+          <cell r="AF19">
+            <v>99.925442005736073</v>
+          </cell>
+          <cell r="AI19">
+            <v>99.43571919588662</v>
+          </cell>
+          <cell r="AL19">
+            <v>99.5851618327587</v>
+          </cell>
+          <cell r="AO19">
+            <v>99.777845618989744</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20">
+            <v>100.0765308784086</v>
+          </cell>
+          <cell r="H20">
+            <v>100.09106513117777</v>
+          </cell>
+          <cell r="K20">
+            <v>100.0105047665852</v>
+          </cell>
+          <cell r="N20">
+            <v>99.629436964666098</v>
+          </cell>
+          <cell r="Q20">
+            <v>99.838453699072787</v>
+          </cell>
+          <cell r="T20">
+            <v>99.579150012602852</v>
+          </cell>
+          <cell r="W20">
+            <v>99.456682342340088</v>
+          </cell>
+          <cell r="Z20">
+            <v>99.787267059012066</v>
+          </cell>
+          <cell r="AC20">
+            <v>99.851687979305694</v>
+          </cell>
+          <cell r="AF20">
+            <v>99.950746666056517</v>
+          </cell>
+          <cell r="AI20">
+            <v>99.436947756535247</v>
+          </cell>
+          <cell r="AL20">
+            <v>99.554391009915037</v>
+          </cell>
+          <cell r="AO20">
+            <v>99.830854847616763</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>100.05733542435091</v>
+          </cell>
+          <cell r="H21">
+            <v>100.04085105246074</v>
+          </cell>
+          <cell r="K21">
+            <v>99.992280064940346</v>
+          </cell>
+          <cell r="N21">
+            <v>99.639839882831581</v>
+          </cell>
+          <cell r="Q21">
+            <v>99.755354062378942</v>
+          </cell>
+          <cell r="T21">
+            <v>99.555602115922412</v>
+          </cell>
+          <cell r="W21">
+            <v>99.369193665467407</v>
+          </cell>
+          <cell r="Z21">
+            <v>99.784858594389746</v>
+          </cell>
+          <cell r="AC21">
+            <v>99.813688638894448</v>
+          </cell>
+          <cell r="AF21">
+            <v>99.873954283592951</v>
+          </cell>
+          <cell r="AI21">
+            <v>99.430608171272638</v>
+          </cell>
+          <cell r="AL21">
+            <v>99.43376215776685</v>
+          </cell>
+          <cell r="AO21">
+            <v>99.788796736834058</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22">
+            <v>99.988950310446398</v>
+          </cell>
+          <cell r="H22">
+            <v>100.00721157183912</v>
+          </cell>
+          <cell r="K22">
+            <v>99.998850860964481</v>
+          </cell>
+          <cell r="N22">
+            <v>99.588174249730585</v>
+          </cell>
+          <cell r="Q22">
+            <v>99.69168766010398</v>
+          </cell>
+          <cell r="T22">
+            <v>99.49114569998244</v>
+          </cell>
+          <cell r="W22">
+            <v>99.374895872993136</v>
+          </cell>
+          <cell r="Z22">
+            <v>99.722291161176983</v>
+          </cell>
+          <cell r="AC22">
+            <v>99.721960926337914</v>
+          </cell>
+          <cell r="AF22">
+            <v>99.870055597785637</v>
+          </cell>
+          <cell r="AI22">
+            <v>99.392561844963851</v>
+          </cell>
+          <cell r="AL22">
+            <v>99.367635216971991</v>
+          </cell>
+          <cell r="AO22">
+            <v>99.688535571218267</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23">
+            <v>99.985366987709057</v>
+          </cell>
+          <cell r="H23">
+            <v>99.9757425418575</v>
+          </cell>
+          <cell r="K23">
+            <v>99.998314973505245</v>
+          </cell>
+          <cell r="N23">
+            <v>99.641854574904244</v>
+          </cell>
+          <cell r="Q23">
+            <v>99.734443189469886</v>
+          </cell>
+          <cell r="T23">
+            <v>99.551918806135077</v>
+          </cell>
+          <cell r="W23">
+            <v>99.514905845455573</v>
+          </cell>
+          <cell r="Z23">
+            <v>99.757690823610844</v>
+          </cell>
+          <cell r="AC23">
+            <v>99.760213978292995</v>
+          </cell>
+          <cell r="AF23">
+            <v>99.938683406323065</v>
+          </cell>
+          <cell r="AI23">
+            <v>99.303629785270857</v>
+          </cell>
+          <cell r="AL23">
+            <v>99.586682850618729</v>
+          </cell>
+          <cell r="AO23">
+            <v>99.675210085551967</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24">
+            <v>99.977828088389174</v>
+          </cell>
+          <cell r="H24">
+            <v>99.992257561557992</v>
+          </cell>
+          <cell r="K24">
+            <v>100.02393220803498</v>
+          </cell>
+          <cell r="N24">
+            <v>99.695713615157715</v>
+          </cell>
+          <cell r="Q24">
+            <v>99.776372884252893</v>
+          </cell>
+          <cell r="T24">
+            <v>99.633049220366686</v>
+          </cell>
+          <cell r="W24">
+            <v>99.444321108748994</v>
+          </cell>
+          <cell r="Z24">
+            <v>99.725033999421058</v>
+          </cell>
+          <cell r="AC24">
+            <v>99.79845162475948</v>
+          </cell>
+          <cell r="AF24">
+            <v>99.938968107531025</v>
+          </cell>
+          <cell r="AI24">
+            <v>99.355463585680312</v>
+          </cell>
+          <cell r="AL24">
+            <v>99.574541381303391</v>
+          </cell>
+          <cell r="AO24">
+            <v>99.724217547460242</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="E25">
+            <v>99.919641251379531</v>
+          </cell>
+          <cell r="H25">
+            <v>99.92095840047439</v>
+          </cell>
+          <cell r="K25">
+            <v>100.01444387988541</v>
+          </cell>
+          <cell r="N25">
+            <v>99.727505434419129</v>
+          </cell>
+          <cell r="Q25">
+            <v>99.741131543116438</v>
+          </cell>
+          <cell r="T25">
+            <v>99.687113705765739</v>
+          </cell>
+          <cell r="W25">
+            <v>99.603111113064145</v>
+          </cell>
+          <cell r="Z25">
+            <v>99.785730096433483</v>
+          </cell>
+          <cell r="AC25">
+            <v>99.773125497252536</v>
+          </cell>
+          <cell r="AF25">
+            <v>99.893200719924934</v>
+          </cell>
+          <cell r="AI25">
+            <v>99.60967684247359</v>
+          </cell>
+          <cell r="AL25">
+            <v>99.630314785749761</v>
+          </cell>
+          <cell r="AO25">
+            <v>99.702508360330668</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="E26">
+            <v>100.03388381233339</v>
+          </cell>
+          <cell r="H26">
+            <v>100.0429552867065</v>
+          </cell>
+          <cell r="K26">
+            <v>100.01788825306258</v>
+          </cell>
+          <cell r="N26">
+            <v>99.813450944800593</v>
+          </cell>
+          <cell r="Q26">
+            <v>99.863363852522838</v>
+          </cell>
+          <cell r="T26">
+            <v>99.813244670284348</v>
+          </cell>
+          <cell r="W26">
+            <v>99.747087644407415</v>
+          </cell>
+          <cell r="Z26">
+            <v>99.896872180775858</v>
+          </cell>
+          <cell r="AC26">
+            <v>99.919337685679579</v>
+          </cell>
+          <cell r="AF26">
+            <v>100.0097467011099</v>
+          </cell>
+          <cell r="AI26">
+            <v>99.67766959339356</v>
+          </cell>
+          <cell r="AL26">
+            <v>99.750935032482829</v>
+          </cell>
+          <cell r="AO26">
+            <v>99.842501579461924</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="E27">
+            <v>99.925668613883019</v>
+          </cell>
+          <cell r="H27">
+            <v>99.969061729816588</v>
+          </cell>
+          <cell r="K27">
+            <v>100.0357161481311</v>
+          </cell>
+          <cell r="N27">
+            <v>99.682306553985072</v>
+          </cell>
+          <cell r="Q27">
+            <v>99.710247095592493</v>
+          </cell>
+          <cell r="T27">
+            <v>99.664178956000598</v>
+          </cell>
+          <cell r="W27">
+            <v>99.547116884572219</v>
+          </cell>
+          <cell r="Z27">
+            <v>99.745662522741441</v>
+          </cell>
+          <cell r="AC27">
+            <v>99.755635093743479</v>
+          </cell>
+          <cell r="AF27">
+            <v>99.937048159925283</v>
+          </cell>
+          <cell r="AI27">
+            <v>99.503564371270187</v>
+          </cell>
+          <cell r="AL27">
+            <v>99.592492462149053</v>
+          </cell>
+          <cell r="AO27">
+            <v>99.699104690512527</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="E28">
+            <v>99.95227693376826</v>
+          </cell>
+          <cell r="H28">
+            <v>99.948204532823667</v>
+          </cell>
+          <cell r="K28">
+            <v>100.01714870371264</v>
+          </cell>
+          <cell r="N28">
+            <v>99.81518052729281</v>
+          </cell>
+          <cell r="Q28">
+            <v>99.773129190272883</v>
+          </cell>
+          <cell r="T28">
+            <v>99.736887597078734</v>
+          </cell>
+          <cell r="W28">
+            <v>99.727304906719425</v>
+          </cell>
+          <cell r="Z28">
+            <v>99.801877112145817</v>
+          </cell>
+          <cell r="AC28">
+            <v>99.83003343624101</v>
+          </cell>
+          <cell r="AF28">
+            <v>99.964304646267195</v>
+          </cell>
+          <cell r="AI28">
+            <v>99.659790694049079</v>
+          </cell>
+          <cell r="AL28">
+            <v>99.601630142081348</v>
+          </cell>
+          <cell r="AO28">
+            <v>99.763926375813227</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="E29">
+            <v>100.04523018543884</v>
+          </cell>
+          <cell r="H29">
+            <v>100.04845713783386</v>
+          </cell>
+          <cell r="K29">
+            <v>100.01121326831985</v>
+          </cell>
+          <cell r="N29">
+            <v>99.86456653686497</v>
+          </cell>
+          <cell r="Q29">
+            <v>99.890690906721673</v>
+          </cell>
+          <cell r="T29">
+            <v>99.836012770812658</v>
+          </cell>
+          <cell r="W29">
+            <v>99.835554123743279</v>
+          </cell>
+          <cell r="Z29">
+            <v>99.899210365614877</v>
+          </cell>
+          <cell r="AC29">
+            <v>99.934607558008025</v>
+          </cell>
+          <cell r="AF29">
+            <v>100.04676975854412</v>
+          </cell>
+          <cell r="AI29">
+            <v>99.769725280259195</v>
+          </cell>
+          <cell r="AL29">
+            <v>99.760845114556219</v>
+          </cell>
+          <cell r="AO29">
+            <v>99.872022239127531</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="E30">
+            <v>100.06770742336714</v>
+          </cell>
+          <cell r="H30">
+            <v>100.07083949919229</v>
+          </cell>
+          <cell r="K30">
+            <v>100.013807826236</v>
+          </cell>
+          <cell r="N30">
+            <v>99.913998465932721</v>
+          </cell>
+          <cell r="Q30">
+            <v>99.91007272299349</v>
+          </cell>
+          <cell r="T30">
+            <v>99.884786199903758</v>
+          </cell>
+          <cell r="W30">
+            <v>99.880798713346721</v>
+          </cell>
+          <cell r="Z30">
+            <v>99.917234773356711</v>
+          </cell>
+          <cell r="AC30">
+            <v>99.965288784580551</v>
+          </cell>
+          <cell r="AF30">
+            <v>100.06568380245663</v>
+          </cell>
+          <cell r="AI30">
+            <v>99.839365397003348</v>
+          </cell>
+          <cell r="AL30">
+            <v>99.819591427830062</v>
+          </cell>
+          <cell r="AO30">
+            <v>99.941332051577689</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="E31">
+            <v>99.877257478460535</v>
+          </cell>
+          <cell r="H31">
+            <v>99.874894288310898</v>
+          </cell>
+          <cell r="K31">
+            <v>100.00528384812331</v>
+          </cell>
+          <cell r="N31">
+            <v>99.723998234137824</v>
+          </cell>
+          <cell r="Q31">
+            <v>99.717973087448058</v>
+          </cell>
+          <cell r="T31">
+            <v>99.682854737047023</v>
+          </cell>
+          <cell r="W31">
+            <v>99.704513392022591</v>
+          </cell>
+          <cell r="Z31">
+            <v>99.73389761561026</v>
+          </cell>
+          <cell r="AC31">
+            <v>99.778313857606292</v>
+          </cell>
+          <cell r="AF31">
+            <v>99.870008856185535</v>
+          </cell>
+          <cell r="AI31">
+            <v>99.688414231020445</v>
+          </cell>
+          <cell r="AL31">
+            <v>99.608564149235292</v>
+          </cell>
+          <cell r="AO31">
+            <v>99.735798290160446</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32">
+            <v>99.921187919491018</v>
+          </cell>
+          <cell r="H32">
+            <v>99.924849430049605</v>
+          </cell>
+          <cell r="K32">
+            <v>100.00732743680963</v>
+          </cell>
+          <cell r="N32">
+            <v>99.775369568430861</v>
+          </cell>
+          <cell r="Q32">
+            <v>99.772942432334148</v>
+          </cell>
+          <cell r="T32">
+            <v>99.74079317770456</v>
+          </cell>
+          <cell r="W32">
+            <v>99.74108645403571</v>
+          </cell>
+          <cell r="Z32">
+            <v>99.757634244286905</v>
+          </cell>
+          <cell r="AC32">
+            <v>99.839350440080736</v>
+          </cell>
+          <cell r="AF32">
+            <v>99.915245022285134</v>
+          </cell>
+          <cell r="AI32">
+            <v>99.729327066427643</v>
+          </cell>
+          <cell r="AL32">
+            <v>99.669421637954898</v>
+          </cell>
+          <cell r="AO32">
+            <v>99.787900047996942</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4519,18 +6645,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="U1:V1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="U1:V1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4553,7 +6679,7 @@
     <col min="12" max="12" width="12.6640625" customWidth="1"/>
     <col min="13" max="13" width="14.21875" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.109375" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.5546875" customWidth="1"/>
     <col min="18" max="18" width="13.44140625" customWidth="1"/>
@@ -4562,78 +6688,78 @@
     <col min="21" max="21" width="15.21875" customWidth="1"/>
     <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="16.5546875" customWidth="1"/>
-    <col min="24" max="24" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.88671875" customWidth="1"/>
     <col min="25" max="25" width="9" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="33.6640625" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.44140625" customWidth="1"/>
     <col min="28" max="28" width="9" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="25.5546875" customWidth="1"/>
     <col min="30" max="30" width="13.33203125" customWidth="1"/>
     <col min="31" max="31" width="9" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="18.6640625" customWidth="1"/>
-    <col min="33" max="33" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="30" customWidth="1"/>
     <col min="34" max="34" width="9" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="17.6640625" customWidth="1"/>
-    <col min="36" max="36" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21" customWidth="1"/>
     <col min="37" max="37" width="9" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="23" customWidth="1"/>
-    <col min="39" max="39" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.44140625" customWidth="1"/>
     <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16" t="s">
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16" t="s">
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="15" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="15"/>
+      <c r="M1" s="17"/>
       <c r="N1" s="12"/>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="15" t="s">
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="15"/>
+      <c r="S1" s="17"/>
       <c r="T1" s="12"/>
       <c r="U1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15" t="s">
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="Y1" s="15"/>
+      <c r="Y1" s="17"/>
       <c r="Z1" s="12"/>
       <c r="AA1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17"/>
       <c r="AD1" s="12" t="s">
         <v>54</v>
       </c>
@@ -4642,22 +6768,22 @@
       <c r="AG1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="15" t="s">
+      <c r="AH1" s="19"/>
+      <c r="AI1" s="19"/>
+      <c r="AJ1" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="15" t="s">
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="19"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="18"/>
       <c r="C2" t="s">
         <v>63</v>
       </c>
@@ -8921,21 +11047,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="AG1:AI1"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="AG1:AI1"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AM1:AO1"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8949,4 +11075,14 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F49AD5-773A-40C5-AC89-4941E6363963}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/ExperimentoCompleto.xlsx
+++ b/ExperimentoCompleto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8590519B-5A11-42E2-BF98-C4FCC05EAB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46C1C98-2194-4FC6-AB2D-D2B30444B04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,140 +18,60 @@
     <sheet name="Planilha2" sheetId="5" r:id="rId3"/>
     <sheet name="Planilha3" sheetId="6" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.100" hidden="1">[1]Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.101" hidden="1">[1]Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.102" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.103" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.104" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.105" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.106" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.107" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.108" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.109" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.110" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.111" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.112" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.113" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.114" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.115" hidden="1">Planilha3!$K:$K</definedName>
-    <definedName name="_xlchart.v1.116" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.117" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.118" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.119" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.120" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.121" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.122" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.123" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.124" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.125" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.126" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.127" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.128" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.129" hidden="1">Planilha3!$K:$K</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Planilha1!$AA$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Planilha1!$AD$1</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Planilha1!$AG$1</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Planilha1!$AJ$1</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Planilha1!$AM$1</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">Planilha1!$F$1</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.53" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.54" hidden="1">Planilha1!$L$1</definedName>
-    <definedName name="_xlchart.v1.55" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.56" hidden="1">Planilha1!$O$1</definedName>
-    <definedName name="_xlchart.v1.57" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.58" hidden="1">Planilha1!$R$1</definedName>
-    <definedName name="_xlchart.v1.59" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.60" hidden="1">Planilha1!$U$1</definedName>
-    <definedName name="_xlchart.v1.61" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.62" hidden="1">Planilha1!$X$1</definedName>
-    <definedName name="_xlchart.v1.63" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.64" hidden="1">Planilha1!$AA$1</definedName>
-    <definedName name="_xlchart.v1.65" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.66" hidden="1">Planilha1!$AD$1</definedName>
-    <definedName name="_xlchart.v1.67" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.68" hidden="1">Planilha1!$AG$1</definedName>
-    <definedName name="_xlchart.v1.69" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.70" hidden="1">Planilha1!$AJ$1</definedName>
-    <definedName name="_xlchart.v1.71" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.72" hidden="1">Planilha1!$AM$1</definedName>
-    <definedName name="_xlchart.v1.73" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.74" hidden="1">Planilha1!$C$1</definedName>
-    <definedName name="_xlchart.v1.75" hidden="1">Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.76" hidden="1">Planilha1!$F$1</definedName>
-    <definedName name="_xlchart.v1.77" hidden="1">Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.78" hidden="1">Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.79" hidden="1">Planilha1!$L$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.80" hidden="1">Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.81" hidden="1">Planilha1!$O$1</definedName>
-    <definedName name="_xlchart.v1.82" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.83" hidden="1">Planilha1!$R$1</definedName>
-    <definedName name="_xlchart.v1.84" hidden="1">Planilha1!$T$3:$T$32</definedName>
-    <definedName name="_xlchart.v1.85" hidden="1">Planilha1!$U$1</definedName>
-    <definedName name="_xlchart.v1.86" hidden="1">Planilha1!$W$3:$W$32</definedName>
-    <definedName name="_xlchart.v1.87" hidden="1">Planilha1!$X$1</definedName>
-    <definedName name="_xlchart.v1.88" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
-    <definedName name="_xlchart.v1.89" hidden="1">[1]Planilha1!$AC$3:$AC$32</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.90" hidden="1">[1]Planilha1!$AF$3:$AF$32</definedName>
-    <definedName name="_xlchart.v1.91" hidden="1">[1]Planilha1!$AI$3:$AI$32</definedName>
-    <definedName name="_xlchart.v1.92" hidden="1">[1]Planilha1!$AL$3:$AL$32</definedName>
-    <definedName name="_xlchart.v1.93" hidden="1">[1]Planilha1!$AO$3:$AO$32</definedName>
-    <definedName name="_xlchart.v1.94" hidden="1">[1]Planilha1!$E$3:$E$32</definedName>
-    <definedName name="_xlchart.v1.95" hidden="1">[1]Planilha1!$H$3:$H$32</definedName>
-    <definedName name="_xlchart.v1.96" hidden="1">[1]Planilha1!$K$3:$K$32</definedName>
-    <definedName name="_xlchart.v1.97" hidden="1">[1]Planilha1!$N$3:$N$32</definedName>
-    <definedName name="_xlchart.v1.98" hidden="1">[1]Planilha1!$Q$3:$Q$32</definedName>
-    <definedName name="_xlchart.v1.99" hidden="1">[1]Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Planilha1!$AA$1</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Planilha1!$C$1</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Planilha1!$F$1</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Planilha1!$L$1</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Planilha1!$O$1</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Planilha1!$R$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Planilha1!$AD$1</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Planilha1!$U$1</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Planilha1!$X$1</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">Planilha3!$K:$K</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">Planilha1!$AC$3:$AC$32</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Planilha1!$AG$1</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">Planilha1!$AF$3:$AF$32</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">Planilha1!$E$3:$E$32</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">Planilha1!$H$3:$H$32</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">Planilha1!$K$3:$K$32</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">Planilha1!$N$3:$N$32</definedName>
+    <definedName name="_xlchart.v1.48" hidden="1">Planilha1!$Q$3:$Q$32</definedName>
+    <definedName name="_xlchart.v1.49" hidden="1">Planilha1!$T$3:$T$32</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Planilha1!$AI$3:$AI$32</definedName>
+    <definedName name="_xlchart.v1.50" hidden="1">Planilha1!$W$3:$W$32</definedName>
+    <definedName name="_xlchart.v1.51" hidden="1">Planilha1!$Z$3:$Z$32</definedName>
+    <definedName name="_xlchart.v1.52" hidden="1">Planilha3!$K:$K</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Planilha1!$AJ$1</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Planilha1!$AL$3:$AL$32</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Planilha1!$AM$1</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Planilha1!$AO$3:$AO$32</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -623,20 +543,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -661,67 +581,67 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.75</cx:f>
+        <cx:f>_xlchart.v1.11</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.77</cx:f>
+        <cx:f>_xlchart.v1.13</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.80</cx:f>
+        <cx:f>_xlchart.v1.16</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.82</cx:f>
+        <cx:f>_xlchart.v1.18</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.84</cx:f>
+        <cx:f>_xlchart.v1.20</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.86</cx:f>
+        <cx:f>_xlchart.v1.22</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="6">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.88</cx:f>
+        <cx:f>_xlchart.v1.24</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="7">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.65</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="8">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.67</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="9">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.69</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="10">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.71</cx:f>
+        <cx:f>_xlchart.v1.7</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="11">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.73</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="12">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.78</cx:f>
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -759,7 +679,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F027B10E-9D4A-42C2-A360-996EFF7CDC29}" formatIdx="0">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.74</cx:f>
+              <cx:f>_xlchart.v1.10</cx:f>
               <cx:v>Padrão</cx:v>
             </cx:txData>
           </cx:tx>
@@ -772,7 +692,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{25922C5E-E129-4246-B9EF-39947B99D9C5}" formatIdx="1">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.76</cx:f>
+              <cx:f>_xlchart.v1.12</cx:f>
               <cx:v>Irace Geral</cx:v>
             </cx:txData>
           </cx:tx>
@@ -785,7 +705,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{8DA59056-C9D5-427C-8AA4-463B2127A648}" formatIdx="2">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.79</cx:f>
+              <cx:f>_xlchart.v1.15</cx:f>
               <cx:v>Configuracao 2 16 7 1656 63656 2,09 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -798,7 +718,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{16C9E66D-30A4-4E13-91E8-ED12B2DB9FDE}" formatIdx="3">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.81</cx:f>
+              <cx:f>_xlchart.v1.17</cx:f>
               <cx:v>Configuracao 2 18 6 2542 73603 2,03 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -811,7 +731,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{F2D5FD8D-045E-43AE-B8C5-E64209EAA869}" formatIdx="4">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.83</cx:f>
+              <cx:f>_xlchart.v1.19</cx:f>
               <cx:v>Configuracao  2 10 16 1644 24767 2,96 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -824,7 +744,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{17BC3A71-22EB-47CC-B52A-284F6EFA9E05}" formatIdx="5">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.85</cx:f>
+              <cx:f>_xlchart.v1.21</cx:f>
               <cx:v>Configuração  2 14 13 2405 43525 0,87 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -837,7 +757,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{5F522F99-7A97-4E23-9D13-87A6755777B4}" formatIdx="6">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.87</cx:f>
+              <cx:f>_xlchart.v1.23</cx:f>
               <cx:v>Configuração  2 14 19 1795 66816 2,77 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -850,7 +770,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{971181E6-C471-4560-9CA5-01A74C68C9D8}" formatIdx="7">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.64</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Configuração  2 20 20 1079 55559 1,08 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -863,7 +783,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{CC135088-7A79-4E02-B37B-A1F392DFA551}" formatIdx="8">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.66</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Configuração  2 18 13 2520 13214 0,67 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -876,7 +796,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{3B130AD7-A71E-4A58-8854-C53F8AA3DE5E}" formatIdx="9">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.68</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Configuração  2 11 16 1797 24360 2,34 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -889,7 +809,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{6D41FE1A-A51D-419E-8C75-BC8EA43C68DD}" formatIdx="10">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.70</cx:f>
+              <cx:f>_xlchart.v1.6</cx:f>
               <cx:v>Configuração  2 11 17 2326 31236 1,35 1</cx:v>
             </cx:txData>
           </cx:tx>
@@ -902,7 +822,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{1324BC5E-E88F-457C-8C14-B953E60EF5EE}" formatIdx="11">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.72</cx:f>
+              <cx:f>_xlchart.v1.8</cx:f>
               <cx:v>Configuração  2 19 6 2851 43903 1,75 0</cx:v>
             </cx:txData>
           </cx:tx>
@@ -997,67 +917,67 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.107</cx:f>
+        <cx:f>_xlchart.v1.30</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.108</cx:f>
+        <cx:f>_xlchart.v1.31</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.109</cx:f>
+        <cx:f>_xlchart.v1.32</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.110</cx:f>
+        <cx:f>_xlchart.v1.33</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.111</cx:f>
+        <cx:f>_xlchart.v1.34</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.112</cx:f>
+        <cx:f>_xlchart.v1.35</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="6">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.113</cx:f>
+        <cx:f>_xlchart.v1.36</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="7">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.114</cx:f>
+        <cx:f>_xlchart.v1.37</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="8">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.102</cx:f>
+        <cx:f>_xlchart.v1.25</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="9">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.103</cx:f>
+        <cx:f>_xlchart.v1.26</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="10">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.104</cx:f>
+        <cx:f>_xlchart.v1.27</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="11">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.105</cx:f>
+        <cx:f>_xlchart.v1.28</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="12">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.106</cx:f>
+        <cx:f>_xlchart.v1.29</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -1066,6 +986,11 @@
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="boxWhisker" uniqueId="{CCC66ADE-7979-48B9-80FE-02C2A5D0741A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>padrão</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1073,6 +998,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{DE12E5D0-3815-4D8A-8DA6-FD1F5C6E976E}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>irace geral</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="1"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1082,8 +1012,7 @@
         <cx:series layoutId="boxWhisker" uniqueId="{7E9AA417-B139-4B19-9688-5CB25A143A26}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.115</cx:f>
-              <cx:v/>
+              <cx:v>irace separado</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="2"/>
@@ -1093,6 +1022,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{19E8D587-E02B-4BB9-83D6-902B45F2F036}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 1</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="3"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1100,6 +1034,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{D65D489C-2013-4BA9-8126-457D63379F9B}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 2</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="4"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1107,6 +1046,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{EC2AB0F9-60BE-40C0-9ACD-6518155B5726}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 3</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="5"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1114,6 +1058,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{D1DE3512-34E7-496F-B4ED-A0D0B3C72EC1}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 4</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="6"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1121,6 +1070,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{946ABE6C-7721-466D-9961-C55B566ACF1B}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 5</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="7"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1128,6 +1082,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{B1FB5F0F-FA22-48CA-BC16-AC23172773E4}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 6</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="8"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1135,6 +1094,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{CBE7198A-C2D2-489E-9260-2A2D343502BC}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 7</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="9"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1142,6 +1106,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{D82772A9-96FE-414A-A0DF-7707B59706A8}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 8</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="10"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1149,6 +1118,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{46544867-521D-41D3-A184-BEE63DF4366C}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 9</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="11"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -1156,6 +1130,11 @@
           </cx:layoutPr>
         </cx:series>
         <cx:series layoutId="boxWhisker" uniqueId="{D0F610E0-E89A-469A-8C52-81F833143880}">
+          <cx:tx>
+            <cx:txData>
+              <cx:v>conf 10</cx:v>
+            </cx:txData>
+          </cx:tx>
           <cx:dataId val="12"/>
           <cx:layoutPr>
             <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
@@ -2473,1259 +2452,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Planilha1"/>
-      <sheetName val="Planilha2"/>
-      <sheetName val="Planilha3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="E3">
-            <v>99.960376813875982</v>
-          </cell>
-          <cell r="H3">
-            <v>99.913143876774512</v>
-          </cell>
-          <cell r="K3">
-            <v>99.947235646652089</v>
-          </cell>
-          <cell r="N3">
-            <v>99.321682542181634</v>
-          </cell>
-          <cell r="Q3">
-            <v>99.497668967085644</v>
-          </cell>
-          <cell r="T3">
-            <v>99.244710348386647</v>
-          </cell>
-          <cell r="W3">
-            <v>99.244885285190719</v>
-          </cell>
-          <cell r="Z3">
-            <v>99.569830398768445</v>
-          </cell>
-          <cell r="AC3">
-            <v>99.633070053443191</v>
-          </cell>
-          <cell r="AF3">
-            <v>99.895562727964517</v>
-          </cell>
-          <cell r="AI3">
-            <v>99.138173834702215</v>
-          </cell>
-          <cell r="AL3">
-            <v>99.153918147069376</v>
-          </cell>
-          <cell r="AO3">
-            <v>99.502829602805988</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="E4">
-            <v>99.961434969717686</v>
-          </cell>
-          <cell r="H4">
-            <v>99.952407246719787</v>
-          </cell>
-          <cell r="K4">
-            <v>99.9882506641882</v>
-          </cell>
-          <cell r="N4">
-            <v>99.449308897127779</v>
-          </cell>
-          <cell r="Q4">
-            <v>99.533363133584004</v>
-          </cell>
-          <cell r="T4">
-            <v>99.455093651670126</v>
-          </cell>
-          <cell r="W4">
-            <v>99.321080171439093</v>
-          </cell>
-          <cell r="Z4">
-            <v>99.649408815615331</v>
-          </cell>
-          <cell r="AC4">
-            <v>99.621975055437233</v>
-          </cell>
-          <cell r="AF4">
-            <v>99.82268850849745</v>
-          </cell>
-          <cell r="AI4">
-            <v>99.209241583620383</v>
-          </cell>
-          <cell r="AL4">
-            <v>99.324761378875124</v>
-          </cell>
-          <cell r="AO4">
-            <v>99.636086350608707</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5">
-            <v>99.967794162691987</v>
-          </cell>
-          <cell r="H5">
-            <v>99.974270336498492</v>
-          </cell>
-          <cell r="K5">
-            <v>100.00026263216964</v>
-          </cell>
-          <cell r="N5">
-            <v>99.55681967356584</v>
-          </cell>
-          <cell r="Q5">
-            <v>99.657812978602365</v>
-          </cell>
-          <cell r="T5">
-            <v>99.389751892530526</v>
-          </cell>
-          <cell r="W5">
-            <v>99.313000481337241</v>
-          </cell>
-          <cell r="Z5">
-            <v>99.621406379906361</v>
-          </cell>
-          <cell r="AC5">
-            <v>99.714785804927146</v>
-          </cell>
-          <cell r="AF5">
-            <v>99.831882028617684</v>
-          </cell>
-          <cell r="AI5">
-            <v>99.168599308624692</v>
-          </cell>
-          <cell r="AL5">
-            <v>99.29348444405548</v>
-          </cell>
-          <cell r="AO5">
-            <v>99.667264691725379</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6">
-            <v>99.895737664768603</v>
-          </cell>
-          <cell r="H6">
-            <v>99.91296893997044</v>
-          </cell>
-          <cell r="K6">
-            <v>99.969529226550193</v>
-          </cell>
-          <cell r="N6">
-            <v>99.201238552572889</v>
-          </cell>
-          <cell r="Q6">
-            <v>99.519973409605782</v>
-          </cell>
-          <cell r="T6">
-            <v>99.239987054676504</v>
-          </cell>
-          <cell r="W6">
-            <v>99.211559824013577</v>
-          </cell>
-          <cell r="Z6">
-            <v>99.544901904187114</v>
-          </cell>
-          <cell r="AC6">
-            <v>99.576915339333667</v>
-          </cell>
-          <cell r="AF6">
-            <v>99.88646601415239</v>
-          </cell>
-          <cell r="AI6">
-            <v>98.987028435977507</v>
-          </cell>
-          <cell r="AL6">
-            <v>99.238937433852016</v>
-          </cell>
-          <cell r="AO6">
-            <v>99.588898510413117</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>99.954214779084126</v>
-          </cell>
-          <cell r="H7">
-            <v>99.990983025326315</v>
-          </cell>
-          <cell r="K7">
-            <v>100.01208652903789</v>
-          </cell>
-          <cell r="N7">
-            <v>99.584168643689438</v>
-          </cell>
-          <cell r="Q7">
-            <v>99.646674662301166</v>
-          </cell>
-          <cell r="T7">
-            <v>99.327841441315257</v>
-          </cell>
-          <cell r="W7">
-            <v>99.273476962942865</v>
-          </cell>
-          <cell r="Z7">
-            <v>99.651314464803164</v>
-          </cell>
-          <cell r="AC7">
-            <v>99.677927671607037</v>
-          </cell>
-          <cell r="AF7">
-            <v>99.869997986500806</v>
-          </cell>
-          <cell r="AI7">
-            <v>99.193637342531233</v>
-          </cell>
-          <cell r="AL7">
-            <v>99.240648171655181</v>
-          </cell>
-          <cell r="AO7">
-            <v>99.588020555200515</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>99.938186211847935</v>
-          </cell>
-          <cell r="H8">
-            <v>99.948867914616429</v>
-          </cell>
-          <cell r="K8">
-            <v>99.982653399145292</v>
-          </cell>
-          <cell r="N8">
-            <v>99.387640744567221</v>
-          </cell>
-          <cell r="Q8">
-            <v>99.616772024445339</v>
-          </cell>
-          <cell r="T8">
-            <v>99.409792144570716</v>
-          </cell>
-          <cell r="W8">
-            <v>99.220585917663328</v>
-          </cell>
-          <cell r="Z8">
-            <v>99.613795156460682</v>
-          </cell>
-          <cell r="AC8">
-            <v>99.683138669515117</v>
-          </cell>
-          <cell r="AF8">
-            <v>99.8796119565027</v>
-          </cell>
-          <cell r="AI8">
-            <v>99.125851471798555</v>
-          </cell>
-          <cell r="AL8">
-            <v>99.292818743761714</v>
-          </cell>
-          <cell r="AO8">
-            <v>99.561174637084775</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>99.966817258527698</v>
-          </cell>
-          <cell r="H9">
-            <v>99.966554598304967</v>
-          </cell>
-          <cell r="K9">
-            <v>99.973374929167676</v>
-          </cell>
-          <cell r="N9">
-            <v>99.394217972963503</v>
-          </cell>
-          <cell r="Q9">
-            <v>99.504797926735307</v>
-          </cell>
-          <cell r="T9">
-            <v>99.332930587658467</v>
-          </cell>
-          <cell r="W9">
-            <v>99.217797856692584</v>
-          </cell>
-          <cell r="Z9">
-            <v>99.636215591510819</v>
-          </cell>
-          <cell r="AC9">
-            <v>99.621243958814873</v>
-          </cell>
-          <cell r="AF9">
-            <v>99.868319675001757</v>
-          </cell>
-          <cell r="AI9">
-            <v>99.167717307557609</v>
-          </cell>
-          <cell r="AL9">
-            <v>99.174458919941159</v>
-          </cell>
-          <cell r="AO9">
-            <v>99.497005673460805</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10">
-            <v>99.95793064241046</v>
-          </cell>
-          <cell r="H10">
-            <v>99.954869462544281</v>
-          </cell>
-          <cell r="K10">
-            <v>100.01128738289341</v>
-          </cell>
-          <cell r="N10">
-            <v>99.448900161805227</v>
-          </cell>
-          <cell r="Q10">
-            <v>99.575807932828965</v>
-          </cell>
-          <cell r="T10">
-            <v>99.37062141951283</v>
-          </cell>
-          <cell r="W10">
-            <v>99.304237547557619</v>
-          </cell>
-          <cell r="Z10">
-            <v>99.621988017667377</v>
-          </cell>
-          <cell r="AC10">
-            <v>99.651900118074082</v>
-          </cell>
-          <cell r="AF10">
-            <v>99.900817772335685</v>
-          </cell>
-          <cell r="AI10">
-            <v>99.237416364192939</v>
-          </cell>
-          <cell r="AL10">
-            <v>99.286832553461323</v>
-          </cell>
-          <cell r="AO10">
-            <v>99.548694625442778</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>99.993531920844703</v>
-          </cell>
-          <cell r="H11">
-            <v>99.973690651003423</v>
-          </cell>
-          <cell r="K11">
-            <v>99.994318211617767</v>
-          </cell>
-          <cell r="N11">
-            <v>99.364817145654143</v>
-          </cell>
-          <cell r="Q11">
-            <v>99.653345919865743</v>
-          </cell>
-          <cell r="T11">
-            <v>99.378277742815186</v>
-          </cell>
-          <cell r="W11">
-            <v>99.223917907838612</v>
-          </cell>
-          <cell r="Z11">
-            <v>99.650636319138528</v>
-          </cell>
-          <cell r="AC11">
-            <v>99.62939654569611</v>
-          </cell>
-          <cell r="AF11">
-            <v>99.885672330606255</v>
-          </cell>
-          <cell r="AI11">
-            <v>99.136948465142297</v>
-          </cell>
-          <cell r="AL11">
-            <v>99.305730368505692</v>
-          </cell>
-          <cell r="AO11">
-            <v>99.541553038249077</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12">
-            <v>99.91910729433576</v>
-          </cell>
-          <cell r="H12">
-            <v>99.936859963795044</v>
-          </cell>
-          <cell r="K12">
-            <v>99.99457361287979</v>
-          </cell>
-          <cell r="N12">
-            <v>99.365363929723912</v>
-          </cell>
-          <cell r="Q12">
-            <v>99.537993336190084</v>
-          </cell>
-          <cell r="T12">
-            <v>99.347873614985701</v>
-          </cell>
-          <cell r="W12">
-            <v>99.285695546091347</v>
-          </cell>
-          <cell r="Z12">
-            <v>99.605680854226975</v>
-          </cell>
-          <cell r="AC12">
-            <v>99.628418263386649</v>
-          </cell>
-          <cell r="AF12">
-            <v>99.826496077796918</v>
-          </cell>
-          <cell r="AI12">
-            <v>99.242669371835348</v>
-          </cell>
-          <cell r="AL12">
-            <v>99.279224129638209</v>
-          </cell>
-          <cell r="AO12">
-            <v>99.554521683617693</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13">
-            <v>100.02957709092482</v>
-          </cell>
-          <cell r="H13">
-            <v>100.01518352096294</v>
-          </cell>
-          <cell r="K13">
-            <v>99.979446266544883</v>
-          </cell>
-          <cell r="N13">
-            <v>99.514304882102735</v>
-          </cell>
-          <cell r="Q13">
-            <v>99.72745698151536</v>
-          </cell>
-          <cell r="T13">
-            <v>99.509547722042143</v>
-          </cell>
-          <cell r="W13">
-            <v>99.301232610623259</v>
-          </cell>
-          <cell r="Z13">
-            <v>99.749335151153886</v>
-          </cell>
-          <cell r="AC13">
-            <v>99.772372996504942</v>
-          </cell>
-          <cell r="AF13">
-            <v>99.883224580695142</v>
-          </cell>
-          <cell r="AI13">
-            <v>99.284637171854925</v>
-          </cell>
-          <cell r="AL13">
-            <v>99.488720339625772</v>
-          </cell>
-          <cell r="AO13">
-            <v>99.72654423194011</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14">
-            <v>99.968509080873631</v>
-          </cell>
-          <cell r="H14">
-            <v>99.95197794254014</v>
-          </cell>
-          <cell r="K14">
-            <v>100.01919065205071</v>
-          </cell>
-          <cell r="N14">
-            <v>99.546366118335925</v>
-          </cell>
-          <cell r="Q14">
-            <v>99.694302761681698</v>
-          </cell>
-          <cell r="T14">
-            <v>99.480794400858599</v>
-          </cell>
-          <cell r="W14">
-            <v>99.403957036452624</v>
-          </cell>
-          <cell r="Z14">
-            <v>99.729760247080961</v>
-          </cell>
-          <cell r="AC14">
-            <v>99.713292699927393</v>
-          </cell>
-          <cell r="AF14">
-            <v>99.837686081697484</v>
-          </cell>
-          <cell r="AI14">
-            <v>99.247215317432463</v>
-          </cell>
-          <cell r="AL14">
-            <v>99.474742345012444</v>
-          </cell>
-          <cell r="AO14">
-            <v>99.701314353521255</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="E15">
-            <v>100.01132010708893</v>
-          </cell>
-          <cell r="H15">
-            <v>100.00221717532024</v>
-          </cell>
-          <cell r="K15">
-            <v>100.00192011841635</v>
-          </cell>
-          <cell r="N15">
-            <v>99.575204635089264</v>
-          </cell>
-          <cell r="Q15">
-            <v>99.726964826285112</v>
-          </cell>
-          <cell r="T15">
-            <v>99.531221905624861</v>
-          </cell>
-          <cell r="W15">
-            <v>99.33850768701069</v>
-          </cell>
-          <cell r="Z15">
-            <v>99.804102549207002</v>
-          </cell>
-          <cell r="AC15">
-            <v>99.772658633815482</v>
-          </cell>
-          <cell r="AF15">
-            <v>99.900910673967459</v>
-          </cell>
-          <cell r="AI15">
-            <v>99.29305864812612</v>
-          </cell>
-          <cell r="AL15">
-            <v>99.476081392127867</v>
-          </cell>
-          <cell r="AO15">
-            <v>99.739438463178786</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>100.01239317733008</v>
-          </cell>
-          <cell r="H16">
-            <v>100.01217251965969</v>
-          </cell>
-          <cell r="K16">
-            <v>100.00544112148638</v>
-          </cell>
-          <cell r="N16">
-            <v>99.590472661726523</v>
-          </cell>
-          <cell r="Q16">
-            <v>99.720449870085289</v>
-          </cell>
-          <cell r="T16">
-            <v>99.525576611427368</v>
-          </cell>
-          <cell r="W16">
-            <v>99.386691978628065</v>
-          </cell>
-          <cell r="Z16">
-            <v>99.780554306713512</v>
-          </cell>
-          <cell r="AC16">
-            <v>99.784902831980816</v>
-          </cell>
-          <cell r="AF16">
-            <v>99.872284599252595</v>
-          </cell>
-          <cell r="AI16">
-            <v>99.343771978388276</v>
-          </cell>
-          <cell r="AL16">
-            <v>99.523660728376015</v>
-          </cell>
-          <cell r="AO16">
-            <v>99.751141321879658</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17">
-            <v>100.00700487721105</v>
-          </cell>
-          <cell r="H17">
-            <v>99.996816777712226</v>
-          </cell>
-          <cell r="K17">
-            <v>99.992597107835408</v>
-          </cell>
-          <cell r="N17">
-            <v>99.563697686389887</v>
-          </cell>
-          <cell r="Q17">
-            <v>99.740052928296279</v>
-          </cell>
-          <cell r="T17">
-            <v>99.598994548270397</v>
-          </cell>
-          <cell r="W17">
-            <v>99.28502927698743</v>
-          </cell>
-          <cell r="Z17">
-            <v>99.69133225009881</v>
-          </cell>
-          <cell r="AC17">
-            <v>99.807325332860032</v>
-          </cell>
-          <cell r="AF17">
-            <v>99.874319861655223</v>
-          </cell>
-          <cell r="AI17">
-            <v>99.293593409944663</v>
-          </cell>
-          <cell r="AL17">
-            <v>99.537604983527956</v>
-          </cell>
-          <cell r="AO17">
-            <v>99.71382912189398</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>100.02320959022396</v>
-          </cell>
-          <cell r="H18">
-            <v>100.02737437299531</v>
-          </cell>
-          <cell r="K18">
-            <v>99.996916889771512</v>
-          </cell>
-          <cell r="N18">
-            <v>99.585452338778452</v>
-          </cell>
-          <cell r="Q18">
-            <v>99.69848268855354</v>
-          </cell>
-          <cell r="T18">
-            <v>99.567717392653435</v>
-          </cell>
-          <cell r="W18">
-            <v>99.38526935713513</v>
-          </cell>
-          <cell r="Z18">
-            <v>99.770713007831688</v>
-          </cell>
-          <cell r="AC18">
-            <v>99.776613101982122</v>
-          </cell>
-          <cell r="AF18">
-            <v>99.896568207648698</v>
-          </cell>
-          <cell r="AI18">
-            <v>99.338634127140324</v>
-          </cell>
-          <cell r="AL18">
-            <v>99.528400719160416</v>
-          </cell>
-          <cell r="AO18">
-            <v>99.729952162357208</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>100.06420302014538</v>
-          </cell>
-          <cell r="H19">
-            <v>100.06211149567268</v>
-          </cell>
-          <cell r="K19">
-            <v>99.996902508085242</v>
-          </cell>
-          <cell r="N19">
-            <v>99.676254172301014</v>
-          </cell>
-          <cell r="Q19">
-            <v>99.767400495246761</v>
-          </cell>
-          <cell r="T19">
-            <v>99.684608569355603</v>
-          </cell>
-          <cell r="W19">
-            <v>99.443453182693929</v>
-          </cell>
-          <cell r="Z19">
-            <v>99.807445366180772</v>
-          </cell>
-          <cell r="AC19">
-            <v>99.852138039728771</v>
-          </cell>
-          <cell r="AF19">
-            <v>99.925442005736073</v>
-          </cell>
-          <cell r="AI19">
-            <v>99.43571919588662</v>
-          </cell>
-          <cell r="AL19">
-            <v>99.5851618327587</v>
-          </cell>
-          <cell r="AO19">
-            <v>99.777845618989744</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20">
-            <v>100.0765308784086</v>
-          </cell>
-          <cell r="H20">
-            <v>100.09106513117777</v>
-          </cell>
-          <cell r="K20">
-            <v>100.0105047665852</v>
-          </cell>
-          <cell r="N20">
-            <v>99.629436964666098</v>
-          </cell>
-          <cell r="Q20">
-            <v>99.838453699072787</v>
-          </cell>
-          <cell r="T20">
-            <v>99.579150012602852</v>
-          </cell>
-          <cell r="W20">
-            <v>99.456682342340088</v>
-          </cell>
-          <cell r="Z20">
-            <v>99.787267059012066</v>
-          </cell>
-          <cell r="AC20">
-            <v>99.851687979305694</v>
-          </cell>
-          <cell r="AF20">
-            <v>99.950746666056517</v>
-          </cell>
-          <cell r="AI20">
-            <v>99.436947756535247</v>
-          </cell>
-          <cell r="AL20">
-            <v>99.554391009915037</v>
-          </cell>
-          <cell r="AO20">
-            <v>99.830854847616763</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>100.05733542435091</v>
-          </cell>
-          <cell r="H21">
-            <v>100.04085105246074</v>
-          </cell>
-          <cell r="K21">
-            <v>99.992280064940346</v>
-          </cell>
-          <cell r="N21">
-            <v>99.639839882831581</v>
-          </cell>
-          <cell r="Q21">
-            <v>99.755354062378942</v>
-          </cell>
-          <cell r="T21">
-            <v>99.555602115922412</v>
-          </cell>
-          <cell r="W21">
-            <v>99.369193665467407</v>
-          </cell>
-          <cell r="Z21">
-            <v>99.784858594389746</v>
-          </cell>
-          <cell r="AC21">
-            <v>99.813688638894448</v>
-          </cell>
-          <cell r="AF21">
-            <v>99.873954283592951</v>
-          </cell>
-          <cell r="AI21">
-            <v>99.430608171272638</v>
-          </cell>
-          <cell r="AL21">
-            <v>99.43376215776685</v>
-          </cell>
-          <cell r="AO21">
-            <v>99.788796736834058</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>99.988950310446398</v>
-          </cell>
-          <cell r="H22">
-            <v>100.00721157183912</v>
-          </cell>
-          <cell r="K22">
-            <v>99.998850860964481</v>
-          </cell>
-          <cell r="N22">
-            <v>99.588174249730585</v>
-          </cell>
-          <cell r="Q22">
-            <v>99.69168766010398</v>
-          </cell>
-          <cell r="T22">
-            <v>99.49114569998244</v>
-          </cell>
-          <cell r="W22">
-            <v>99.374895872993136</v>
-          </cell>
-          <cell r="Z22">
-            <v>99.722291161176983</v>
-          </cell>
-          <cell r="AC22">
-            <v>99.721960926337914</v>
-          </cell>
-          <cell r="AF22">
-            <v>99.870055597785637</v>
-          </cell>
-          <cell r="AI22">
-            <v>99.392561844963851</v>
-          </cell>
-          <cell r="AL22">
-            <v>99.367635216971991</v>
-          </cell>
-          <cell r="AO22">
-            <v>99.688535571218267</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="E23">
-            <v>99.985366987709057</v>
-          </cell>
-          <cell r="H23">
-            <v>99.9757425418575</v>
-          </cell>
-          <cell r="K23">
-            <v>99.998314973505245</v>
-          </cell>
-          <cell r="N23">
-            <v>99.641854574904244</v>
-          </cell>
-          <cell r="Q23">
-            <v>99.734443189469886</v>
-          </cell>
-          <cell r="T23">
-            <v>99.551918806135077</v>
-          </cell>
-          <cell r="W23">
-            <v>99.514905845455573</v>
-          </cell>
-          <cell r="Z23">
-            <v>99.757690823610844</v>
-          </cell>
-          <cell r="AC23">
-            <v>99.760213978292995</v>
-          </cell>
-          <cell r="AF23">
-            <v>99.938683406323065</v>
-          </cell>
-          <cell r="AI23">
-            <v>99.303629785270857</v>
-          </cell>
-          <cell r="AL23">
-            <v>99.586682850618729</v>
-          </cell>
-          <cell r="AO23">
-            <v>99.675210085551967</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="E24">
-            <v>99.977828088389174</v>
-          </cell>
-          <cell r="H24">
-            <v>99.992257561557992</v>
-          </cell>
-          <cell r="K24">
-            <v>100.02393220803498</v>
-          </cell>
-          <cell r="N24">
-            <v>99.695713615157715</v>
-          </cell>
-          <cell r="Q24">
-            <v>99.776372884252893</v>
-          </cell>
-          <cell r="T24">
-            <v>99.633049220366686</v>
-          </cell>
-          <cell r="W24">
-            <v>99.444321108748994</v>
-          </cell>
-          <cell r="Z24">
-            <v>99.725033999421058</v>
-          </cell>
-          <cell r="AC24">
-            <v>99.79845162475948</v>
-          </cell>
-          <cell r="AF24">
-            <v>99.938968107531025</v>
-          </cell>
-          <cell r="AI24">
-            <v>99.355463585680312</v>
-          </cell>
-          <cell r="AL24">
-            <v>99.574541381303391</v>
-          </cell>
-          <cell r="AO24">
-            <v>99.724217547460242</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="E25">
-            <v>99.919641251379531</v>
-          </cell>
-          <cell r="H25">
-            <v>99.92095840047439</v>
-          </cell>
-          <cell r="K25">
-            <v>100.01444387988541</v>
-          </cell>
-          <cell r="N25">
-            <v>99.727505434419129</v>
-          </cell>
-          <cell r="Q25">
-            <v>99.741131543116438</v>
-          </cell>
-          <cell r="T25">
-            <v>99.687113705765739</v>
-          </cell>
-          <cell r="W25">
-            <v>99.603111113064145</v>
-          </cell>
-          <cell r="Z25">
-            <v>99.785730096433483</v>
-          </cell>
-          <cell r="AC25">
-            <v>99.773125497252536</v>
-          </cell>
-          <cell r="AF25">
-            <v>99.893200719924934</v>
-          </cell>
-          <cell r="AI25">
-            <v>99.60967684247359</v>
-          </cell>
-          <cell r="AL25">
-            <v>99.630314785749761</v>
-          </cell>
-          <cell r="AO25">
-            <v>99.702508360330668</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="E26">
-            <v>100.03388381233339</v>
-          </cell>
-          <cell r="H26">
-            <v>100.0429552867065</v>
-          </cell>
-          <cell r="K26">
-            <v>100.01788825306258</v>
-          </cell>
-          <cell r="N26">
-            <v>99.813450944800593</v>
-          </cell>
-          <cell r="Q26">
-            <v>99.863363852522838</v>
-          </cell>
-          <cell r="T26">
-            <v>99.813244670284348</v>
-          </cell>
-          <cell r="W26">
-            <v>99.747087644407415</v>
-          </cell>
-          <cell r="Z26">
-            <v>99.896872180775858</v>
-          </cell>
-          <cell r="AC26">
-            <v>99.919337685679579</v>
-          </cell>
-          <cell r="AF26">
-            <v>100.0097467011099</v>
-          </cell>
-          <cell r="AI26">
-            <v>99.67766959339356</v>
-          </cell>
-          <cell r="AL26">
-            <v>99.750935032482829</v>
-          </cell>
-          <cell r="AO26">
-            <v>99.842501579461924</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="E27">
-            <v>99.925668613883019</v>
-          </cell>
-          <cell r="H27">
-            <v>99.969061729816588</v>
-          </cell>
-          <cell r="K27">
-            <v>100.0357161481311</v>
-          </cell>
-          <cell r="N27">
-            <v>99.682306553985072</v>
-          </cell>
-          <cell r="Q27">
-            <v>99.710247095592493</v>
-          </cell>
-          <cell r="T27">
-            <v>99.664178956000598</v>
-          </cell>
-          <cell r="W27">
-            <v>99.547116884572219</v>
-          </cell>
-          <cell r="Z27">
-            <v>99.745662522741441</v>
-          </cell>
-          <cell r="AC27">
-            <v>99.755635093743479</v>
-          </cell>
-          <cell r="AF27">
-            <v>99.937048159925283</v>
-          </cell>
-          <cell r="AI27">
-            <v>99.503564371270187</v>
-          </cell>
-          <cell r="AL27">
-            <v>99.592492462149053</v>
-          </cell>
-          <cell r="AO27">
-            <v>99.699104690512527</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="E28">
-            <v>99.95227693376826</v>
-          </cell>
-          <cell r="H28">
-            <v>99.948204532823667</v>
-          </cell>
-          <cell r="K28">
-            <v>100.01714870371264</v>
-          </cell>
-          <cell r="N28">
-            <v>99.81518052729281</v>
-          </cell>
-          <cell r="Q28">
-            <v>99.773129190272883</v>
-          </cell>
-          <cell r="T28">
-            <v>99.736887597078734</v>
-          </cell>
-          <cell r="W28">
-            <v>99.727304906719425</v>
-          </cell>
-          <cell r="Z28">
-            <v>99.801877112145817</v>
-          </cell>
-          <cell r="AC28">
-            <v>99.83003343624101</v>
-          </cell>
-          <cell r="AF28">
-            <v>99.964304646267195</v>
-          </cell>
-          <cell r="AI28">
-            <v>99.659790694049079</v>
-          </cell>
-          <cell r="AL28">
-            <v>99.601630142081348</v>
-          </cell>
-          <cell r="AO28">
-            <v>99.763926375813227</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="E29">
-            <v>100.04523018543884</v>
-          </cell>
-          <cell r="H29">
-            <v>100.04845713783386</v>
-          </cell>
-          <cell r="K29">
-            <v>100.01121326831985</v>
-          </cell>
-          <cell r="N29">
-            <v>99.86456653686497</v>
-          </cell>
-          <cell r="Q29">
-            <v>99.890690906721673</v>
-          </cell>
-          <cell r="T29">
-            <v>99.836012770812658</v>
-          </cell>
-          <cell r="W29">
-            <v>99.835554123743279</v>
-          </cell>
-          <cell r="Z29">
-            <v>99.899210365614877</v>
-          </cell>
-          <cell r="AC29">
-            <v>99.934607558008025</v>
-          </cell>
-          <cell r="AF29">
-            <v>100.04676975854412</v>
-          </cell>
-          <cell r="AI29">
-            <v>99.769725280259195</v>
-          </cell>
-          <cell r="AL29">
-            <v>99.760845114556219</v>
-          </cell>
-          <cell r="AO29">
-            <v>99.872022239127531</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="E30">
-            <v>100.06770742336714</v>
-          </cell>
-          <cell r="H30">
-            <v>100.07083949919229</v>
-          </cell>
-          <cell r="K30">
-            <v>100.013807826236</v>
-          </cell>
-          <cell r="N30">
-            <v>99.913998465932721</v>
-          </cell>
-          <cell r="Q30">
-            <v>99.91007272299349</v>
-          </cell>
-          <cell r="T30">
-            <v>99.884786199903758</v>
-          </cell>
-          <cell r="W30">
-            <v>99.880798713346721</v>
-          </cell>
-          <cell r="Z30">
-            <v>99.917234773356711</v>
-          </cell>
-          <cell r="AC30">
-            <v>99.965288784580551</v>
-          </cell>
-          <cell r="AF30">
-            <v>100.06568380245663</v>
-          </cell>
-          <cell r="AI30">
-            <v>99.839365397003348</v>
-          </cell>
-          <cell r="AL30">
-            <v>99.819591427830062</v>
-          </cell>
-          <cell r="AO30">
-            <v>99.941332051577689</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="E31">
-            <v>99.877257478460535</v>
-          </cell>
-          <cell r="H31">
-            <v>99.874894288310898</v>
-          </cell>
-          <cell r="K31">
-            <v>100.00528384812331</v>
-          </cell>
-          <cell r="N31">
-            <v>99.723998234137824</v>
-          </cell>
-          <cell r="Q31">
-            <v>99.717973087448058</v>
-          </cell>
-          <cell r="T31">
-            <v>99.682854737047023</v>
-          </cell>
-          <cell r="W31">
-            <v>99.704513392022591</v>
-          </cell>
-          <cell r="Z31">
-            <v>99.73389761561026</v>
-          </cell>
-          <cell r="AC31">
-            <v>99.778313857606292</v>
-          </cell>
-          <cell r="AF31">
-            <v>99.870008856185535</v>
-          </cell>
-          <cell r="AI31">
-            <v>99.688414231020445</v>
-          </cell>
-          <cell r="AL31">
-            <v>99.608564149235292</v>
-          </cell>
-          <cell r="AO31">
-            <v>99.735798290160446</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="E32">
-            <v>99.921187919491018</v>
-          </cell>
-          <cell r="H32">
-            <v>99.924849430049605</v>
-          </cell>
-          <cell r="K32">
-            <v>100.00732743680963</v>
-          </cell>
-          <cell r="N32">
-            <v>99.775369568430861</v>
-          </cell>
-          <cell r="Q32">
-            <v>99.772942432334148</v>
-          </cell>
-          <cell r="T32">
-            <v>99.74079317770456</v>
-          </cell>
-          <cell r="W32">
-            <v>99.74108645403571</v>
-          </cell>
-          <cell r="Z32">
-            <v>99.757634244286905</v>
-          </cell>
-          <cell r="AC32">
-            <v>99.839350440080736</v>
-          </cell>
-          <cell r="AF32">
-            <v>99.915245022285134</v>
-          </cell>
-          <cell r="AI32">
-            <v>99.729327066427643</v>
-          </cell>
-          <cell r="AL32">
-            <v>99.669421637954898</v>
-          </cell>
-          <cell r="AO32">
-            <v>99.787900047996942</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6645,18 +5371,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="U1:V1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6709,57 +5435,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19" t="s">
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19" t="s">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="17" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="17"/>
+      <c r="M1" s="15"/>
       <c r="N1" s="12"/>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="17" t="s">
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="17"/>
+      <c r="S1" s="15"/>
       <c r="T1" s="12"/>
       <c r="U1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="Y1" s="17"/>
+      <c r="Y1" s="15"/>
       <c r="Z1" s="12"/>
       <c r="AA1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
       <c r="AD1" s="12" t="s">
         <v>54</v>
       </c>
@@ -6768,22 +5494,22 @@
       <c r="AG1" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="17" t="s">
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17" t="s">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="18"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="19"/>
       <c r="C2" t="s">
         <v>63</v>
       </c>
@@ -11047,21 +9773,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
